--- a/exports/commodities-without-images.xlsx
+++ b/exports/commodities-without-images.xlsx
@@ -433,7 +433,7 @@
         <v>1366</v>
       </c>
       <c r="B2" t="str">
-        <v>31200 View | Edit | Add opening stock | Delete</v>
+        <v>31200</v>
       </c>
       <c r="C2" t="str">
         <v>ZANAHORIA QUEBRADA ARP</v>
@@ -462,7 +462,7 @@
         <v>1365</v>
       </c>
       <c r="B3" t="str">
-        <v>21962 View | Edit | Add opening stock | Delete</v>
+        <v>21962</v>
       </c>
       <c r="C3" t="str">
         <v>ZANAHORIA POLVO ARP</v>
@@ -491,7 +491,7 @@
         <v>1364</v>
       </c>
       <c r="B4" t="str">
-        <v>95687 View | Edit | Add opening stock | Delete</v>
+        <v>95687</v>
       </c>
       <c r="C4" t="str">
         <v>ZANAHORIA MEDIANA PZ</v>
@@ -520,7 +520,7 @@
         <v>1363</v>
       </c>
       <c r="B5" t="str">
-        <v>77050 View | Edit | Add opening stock | Delete</v>
+        <v>77050</v>
       </c>
       <c r="C5" t="str">
         <v>ZANAHORIA MEDIANA KG</v>
@@ -549,7 +549,7 @@
         <v>1361</v>
       </c>
       <c r="B6" t="str">
-        <v>83720 View | Edit | Add opening stock | Delete</v>
+        <v>83720</v>
       </c>
       <c r="C6" t="str">
         <v>ZANAHORIA LEÑA KG</v>
@@ -578,7 +578,7 @@
         <v>1360</v>
       </c>
       <c r="B7" t="str">
-        <v>66429 View | Edit | Add opening stock | Delete</v>
+        <v>66429</v>
       </c>
       <c r="C7" t="str">
         <v>ZANAHORIA LEÑA ARP</v>
@@ -607,7 +607,7 @@
         <v>1358</v>
       </c>
       <c r="B8" t="str">
-        <v>29158 View | Edit | Add opening stock | Delete</v>
+        <v>29158</v>
       </c>
       <c r="C8" t="str">
         <v>YUKA TAMARINDO</v>
@@ -636,7 +636,7 @@
         <v>1357</v>
       </c>
       <c r="B9" t="str">
-        <v>71992 View | Edit | Add opening stock | Delete</v>
+        <v>71992</v>
       </c>
       <c r="C9" t="str">
         <v>YOGURTH NATURAL</v>
@@ -665,7 +665,7 @@
         <v>1356</v>
       </c>
       <c r="B10" t="str">
-        <v>43513 View | Edit | Add opening stock | Delete</v>
+        <v>43513</v>
       </c>
       <c r="C10" t="str">
         <v>YOGURT OIKOS</v>
@@ -694,7 +694,7 @@
         <v>1354</v>
       </c>
       <c r="B11" t="str">
-        <v>42320 View | Edit | Add opening stock | Delete</v>
+        <v>42320</v>
       </c>
       <c r="C11" t="str">
         <v>XONOCOSTLE</v>
@@ -723,7 +723,7 @@
         <v>1352</v>
       </c>
       <c r="B12" t="str">
-        <v>73601 View | Edit | Add opening stock | Delete</v>
+        <v>73601</v>
       </c>
       <c r="C12" t="str">
         <v>VITROLERO</v>
@@ -752,7 +752,7 @@
         <v>1351</v>
       </c>
       <c r="B13" t="str">
-        <v>96228 View | Edit | Add opening stock | Delete</v>
+        <v>96228</v>
       </c>
       <c r="C13" t="str">
         <v>VINO TINTO</v>
@@ -781,7 +781,7 @@
         <v>1350</v>
       </c>
       <c r="B14" t="str">
-        <v>87066 View | Edit | Add opening stock | Delete</v>
+        <v>87066</v>
       </c>
       <c r="C14" t="str">
         <v>VINAGRE Galón</v>
@@ -810,7 +810,7 @@
         <v>1349</v>
       </c>
       <c r="B15" t="str">
-        <v>52407 View | Edit | Add opening stock | Delete</v>
+        <v>52407</v>
       </c>
       <c r="C15" t="str">
         <v>VINAGRE DE VINO TINTO</v>
@@ -839,7 +839,7 @@
         <v>1348</v>
       </c>
       <c r="B16" t="str">
-        <v>21180 View | Edit | Add opening stock | Delete</v>
+        <v>21180</v>
       </c>
       <c r="C16" t="str">
         <v>VINAGRE DE VINO BLANCO</v>
@@ -868,7 +868,7 @@
         <v>1347</v>
       </c>
       <c r="B17" t="str">
-        <v>84260 View | Edit | Add opening stock | Delete</v>
+        <v>84260</v>
       </c>
       <c r="C17" t="str">
         <v>VINAGRE DE JEREZ</v>
@@ -897,7 +897,7 @@
         <v>1346</v>
       </c>
       <c r="B18" t="str">
-        <v>26056 View | Edit | Add opening stock | Delete</v>
+        <v>26056</v>
       </c>
       <c r="C18" t="str">
         <v>VINAGRE BALSAMICO 1Litro</v>
@@ -926,7 +926,7 @@
         <v>1345</v>
       </c>
       <c r="B19" t="str">
-        <v>16543 View | Edit | Add opening stock | Delete</v>
+        <v>16543</v>
       </c>
       <c r="C19" t="str">
         <v>VINAGRE BALSAMICO</v>
@@ -955,7 +955,7 @@
         <v>1340</v>
       </c>
       <c r="B20" t="str">
-        <v>74791 View | Edit | Add opening stock | Delete</v>
+        <v>74791</v>
       </c>
       <c r="C20" t="str">
         <v>VASOS 2 OZ</v>
@@ -984,7 +984,7 @@
         <v>1339</v>
       </c>
       <c r="B21" t="str">
-        <v>53429 View | Edit | Add opening stock | Delete</v>
+        <v>53429</v>
       </c>
       <c r="C21" t="str">
         <v>VASO TERMICO LITRO</v>
@@ -1013,7 +1013,7 @@
         <v>1338</v>
       </c>
       <c r="B22" t="str">
-        <v>88325 View | Edit | Add opening stock | Delete</v>
+        <v>88325</v>
       </c>
       <c r="C22" t="str">
         <v>VASO TERMICO 8 CJ</v>
@@ -1042,7 +1042,7 @@
         <v>1337</v>
       </c>
       <c r="B23" t="str">
-        <v>62431 View | Edit | Add opening stock | Delete</v>
+        <v>62431</v>
       </c>
       <c r="C23" t="str">
         <v>VASO TERMICO 1/2 CJ</v>
@@ -1071,7 +1071,7 @@
         <v>1336</v>
       </c>
       <c r="B24" t="str">
-        <v>25593 View | Edit | Add opening stock | Delete</v>
+        <v>25593</v>
       </c>
       <c r="C24" t="str">
         <v>VASO TERMICO 1/2</v>
@@ -1100,7 +1100,7 @@
         <v>1335</v>
       </c>
       <c r="B25" t="str">
-        <v>64170 View | Edit | Add opening stock | Delete</v>
+        <v>64170</v>
       </c>
       <c r="C25" t="str">
         <v>VASO TERMICO #8 PQ</v>
@@ -1129,7 +1129,7 @@
         <v>1334</v>
       </c>
       <c r="B26" t="str">
-        <v>79320 View | Edit | Add opening stock | Delete</v>
+        <v>79320</v>
       </c>
       <c r="C26" t="str">
         <v>VASO TERMICO #6</v>
@@ -1158,7 +1158,7 @@
         <v>1333</v>
       </c>
       <c r="B27" t="str">
-        <v>93096 View | Edit | Add opening stock | Delete</v>
+        <v>93096</v>
       </c>
       <c r="C27" t="str">
         <v>VASO TERMICO #10</v>
@@ -1187,7 +1187,7 @@
         <v>1331</v>
       </c>
       <c r="B28" t="str">
-        <v>52696 View | Edit | Add opening stock | Delete</v>
+        <v>52696</v>
       </c>
       <c r="C28" t="str">
         <v>VASO L4</v>
@@ -1216,7 +1216,7 @@
         <v>1330</v>
       </c>
       <c r="B29" t="str">
-        <v>41894 View | Edit | Add opening stock | Delete</v>
+        <v>41894</v>
       </c>
       <c r="C29" t="str">
         <v>VASO D CarteraON</v>
@@ -1245,7 +1245,7 @@
         <v>1329</v>
       </c>
       <c r="B30" t="str">
-        <v>87140 View | Edit | Add opening stock | Delete</v>
+        <v>87140</v>
       </c>
       <c r="C30" t="str">
         <v>VASO 7 A</v>
@@ -1274,7 +1274,7 @@
         <v>1328</v>
       </c>
       <c r="B31" t="str">
-        <v>16672 View | Edit | Add opening stock | Delete</v>
+        <v>16672</v>
       </c>
       <c r="C31" t="str">
         <v>VASO 6 CAJA</v>
@@ -1303,7 +1303,7 @@
         <v>1326</v>
       </c>
       <c r="B32" t="str">
-        <v>68017 View | Edit | Add opening stock | Delete</v>
+        <v>68017</v>
       </c>
       <c r="C32" t="str">
         <v>VASO 2 OZ CJ</v>
@@ -1332,7 +1332,7 @@
         <v>1324</v>
       </c>
       <c r="B33" t="str">
-        <v>32120 View | Edit | Add opening stock | Delete</v>
+        <v>32120</v>
       </c>
       <c r="C33" t="str">
         <v>VASO #14 CAJA</v>
@@ -1361,7 +1361,7 @@
         <v>1323</v>
       </c>
       <c r="B34" t="str">
-        <v>45283 View | Edit | Add opening stock | Delete</v>
+        <v>45283</v>
       </c>
       <c r="C34" t="str">
         <v>VASO #14</v>
@@ -1390,7 +1390,7 @@
         <v>1322</v>
       </c>
       <c r="B35" t="str">
-        <v>88125 View | Edit | Add opening stock | Delete</v>
+        <v>88125</v>
       </c>
       <c r="C35" t="str">
         <v>VASO # 8</v>
@@ -1419,7 +1419,7 @@
         <v>1321</v>
       </c>
       <c r="B36" t="str">
-        <v>39506 View | Edit | Add opening stock | Delete</v>
+        <v>39506</v>
       </c>
       <c r="C36" t="str">
         <v>VASO # 6</v>
@@ -1448,7 +1448,7 @@
         <v>1320</v>
       </c>
       <c r="B37" t="str">
-        <v>58478 View | Edit | Add opening stock | Delete</v>
+        <v>58478</v>
       </c>
       <c r="C37" t="str">
         <v>VASO</v>
@@ -1477,7 +1477,7 @@
         <v>1318</v>
       </c>
       <c r="B38" t="str">
-        <v>77578 View | Edit | Add opening stock | Delete</v>
+        <v>77578</v>
       </c>
       <c r="C38" t="str">
         <v>VAINAS DE VAINILLA</v>
@@ -1506,7 +1506,7 @@
         <v>1317</v>
       </c>
       <c r="B39" t="str">
-        <v>93259 View | Edit | Add opening stock | Delete</v>
+        <v>93259</v>
       </c>
       <c r="C39" t="str">
         <v>UVA VERDE S/S KG</v>
@@ -1535,7 +1535,7 @@
         <v>1315</v>
       </c>
       <c r="B40" t="str">
-        <v>39950 View | Edit | Add opening stock | Delete</v>
+        <v>39950</v>
       </c>
       <c r="C40" t="str">
         <v>UVA VDE S/S CJ</v>
@@ -1564,7 +1564,7 @@
         <v>1303</v>
       </c>
       <c r="B41" t="str">
-        <v>10994 View | Edit | Add opening stock | Delete</v>
+        <v>10994</v>
       </c>
       <c r="C41" t="str">
         <v>TORTILLA RASPADA</v>
@@ -1593,7 +1593,7 @@
         <v>1302</v>
       </c>
       <c r="B42" t="str">
-        <v>72876 View | Edit | Add opening stock | Delete</v>
+        <v>72876</v>
       </c>
       <c r="C42" t="str">
         <v>TORTILLA MANO CH</v>
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="B43" t="str">
-        <v>12821 View | Edit | Add opening stock | Delete</v>
+        <v>12821</v>
       </c>
       <c r="C43" t="str">
         <v>TORTILLA HARINA LETY</v>
@@ -1651,7 +1651,7 @@
         <v>1300</v>
       </c>
       <c r="B44" t="str">
-        <v>45655 View | Edit | Add opening stock | Delete</v>
+        <v>45655</v>
       </c>
       <c r="C44" t="str">
         <v>TORTILLA HARINA BURRITOS</v>
@@ -1680,7 +1680,7 @@
         <v>1298</v>
       </c>
       <c r="B45" t="str">
-        <v>83512 View | Edit | Add opening stock | Delete</v>
+        <v>83512</v>
       </c>
       <c r="C45" t="str">
         <v>TORTILLA DE HARINA</v>
@@ -1709,7 +1709,7 @@
         <v>1295</v>
       </c>
       <c r="B46" t="str">
-        <v>97511 View | Edit | Add opening stock | Delete</v>
+        <v>97511</v>
       </c>
       <c r="C46" t="str">
         <v>TOPO CHICO D 1.5</v>
@@ -1738,7 +1738,7 @@
         <v>1291</v>
       </c>
       <c r="B47" t="str">
-        <v>28168 View | Edit | Add opening stock | Delete</v>
+        <v>28168</v>
       </c>
       <c r="C47" t="str">
         <v>TOMATE VERDE PELADO PZ</v>
@@ -1767,7 +1767,7 @@
         <v>1290</v>
       </c>
       <c r="B48" t="str">
-        <v>69848 View | Edit | Add opening stock | Delete</v>
+        <v>69848</v>
       </c>
       <c r="C48" t="str">
         <v>TOMATE VERDE PELADO KG</v>
@@ -1796,7 +1796,7 @@
         <v>1289</v>
       </c>
       <c r="B49" t="str">
-        <v>33883 View | Edit | Add opening stock | Delete</v>
+        <v>33883</v>
       </c>
       <c r="C49" t="str">
         <v>TOMATE VERDE CON CASCARA PZ</v>
@@ -1825,7 +1825,7 @@
         <v>1288</v>
       </c>
       <c r="B50" t="str">
-        <v>51771 View | Edit | Add opening stock | Delete</v>
+        <v>51771</v>
       </c>
       <c r="C50" t="str">
         <v>TOMATE VERDE CON CASCARA KG</v>
@@ -1854,7 +1854,7 @@
         <v>1287</v>
       </c>
       <c r="B51" t="str">
-        <v>51240 View | Edit | Add opening stock | Delete</v>
+        <v>51240</v>
       </c>
       <c r="C51" t="str">
         <v>TOMATE MORADO PELADO KG</v>
@@ -1883,7 +1883,7 @@
         <v>1286</v>
       </c>
       <c r="B52" t="str">
-        <v>17856 View | Edit | Add opening stock | Delete</v>
+        <v>17856</v>
       </c>
       <c r="C52" t="str">
         <v>TOMATE MORADO KG</v>
@@ -1912,7 +1912,7 @@
         <v>1285</v>
       </c>
       <c r="B53" t="str">
-        <v>66848 View | Edit | Add opening stock | Delete</v>
+        <v>66848</v>
       </c>
       <c r="C53" t="str">
         <v>TOMATE DESHIDRATADO</v>
@@ -1941,7 +1941,7 @@
         <v>1284</v>
       </c>
       <c r="B54" t="str">
-        <v>53161 View | Edit | Add opening stock | Delete</v>
+        <v>53161</v>
       </c>
       <c r="C54" t="str">
         <v>TOMATE CHERRY UVA KG</v>
@@ -1970,7 +1970,7 @@
         <v>1283</v>
       </c>
       <c r="B55" t="str">
-        <v>59419 View | Edit | Add opening stock | Delete</v>
+        <v>59419</v>
       </c>
       <c r="C55" t="str">
         <v>TOMATE CHERRY UVA CJ</v>
@@ -1999,7 +1999,7 @@
         <v>1282</v>
       </c>
       <c r="B56" t="str">
-        <v>72921 View | Edit | Add opening stock | Delete</v>
+        <v>72921</v>
       </c>
       <c r="C56" t="str">
         <v>TOMATE CHERRY BUR CJ</v>
@@ -2028,7 +2028,7 @@
         <v>1276</v>
       </c>
       <c r="B57" t="str">
-        <v>78893 View | Edit | Add opening stock | Delete</v>
+        <v>78893</v>
       </c>
       <c r="C57" t="str">
         <v>TE LIMON ManojoO</v>
@@ -2057,7 +2057,7 @@
         <v>1267</v>
       </c>
       <c r="B58" t="str">
-        <v>92239 View | Edit | Add opening stock | Delete</v>
+        <v>92239</v>
       </c>
       <c r="C58" t="str">
         <v>TAMARINDO PEL</v>
@@ -2086,7 +2086,7 @@
         <v>1266</v>
       </c>
       <c r="B59" t="str">
-        <v>77766 View | Edit | Add opening stock | Delete</v>
+        <v>77766</v>
       </c>
       <c r="C59" t="str">
         <v>TAJIN</v>
@@ -2115,7 +2115,7 @@
         <v>1260</v>
       </c>
       <c r="B60" t="str">
-        <v>12896 View | Edit | Add opening stock | Delete</v>
+        <v>12896</v>
       </c>
       <c r="C60" t="str">
         <v>SPRING MIX Earthbound Farm</v>
@@ -2144,7 +2144,7 @@
         <v>1258</v>
       </c>
       <c r="B61" t="str">
-        <v>88785 View | Edit | Add opening stock | Delete</v>
+        <v>88785</v>
       </c>
       <c r="C61" t="str">
         <v>SOYA TEXTURIZADA</v>
@@ -2173,7 +2173,7 @@
         <v>1257</v>
       </c>
       <c r="B62" t="str">
-        <v>63932 View | Edit | Add opening stock | Delete</v>
+        <v>63932</v>
       </c>
       <c r="C62" t="str">
         <v>SIRLON</v>
@@ -2202,7 +2202,7 @@
         <v>1256</v>
       </c>
       <c r="B63" t="str">
-        <v>91021 View | Edit | Add opening stock | Delete</v>
+        <v>91021</v>
       </c>
       <c r="C63" t="str">
         <v>SERVILLETA VELVET CJ</v>
@@ -2231,7 +2231,7 @@
         <v>1255</v>
       </c>
       <c r="B64" t="str">
-        <v>22140 View | Edit | Add opening stock | Delete</v>
+        <v>22140</v>
       </c>
       <c r="C64" t="str">
         <v>SERVILLETA PQTE</v>
@@ -2260,7 +2260,7 @@
         <v>1254</v>
       </c>
       <c r="B65" t="str">
-        <v>33502 View | Edit | Add opening stock | Delete</v>
+        <v>33502</v>
       </c>
       <c r="C65" t="str">
         <v>SERVILLETA CAFE</v>
@@ -2289,7 +2289,7 @@
         <v>1253</v>
       </c>
       <c r="B66" t="str">
-        <v>48826 View | Edit | Add opening stock | Delete</v>
+        <v>48826</v>
       </c>
       <c r="C66" t="str">
         <v>SEMILLA GIRASOL PELADA</v>
@@ -2318,7 +2318,7 @@
         <v>1252</v>
       </c>
       <c r="B67" t="str">
-        <v>52042 View | Edit | Add opening stock | Delete</v>
+        <v>52042</v>
       </c>
       <c r="C67" t="str">
         <v>SEMILLA</v>
@@ -2347,7 +2347,7 @@
         <v>1251</v>
       </c>
       <c r="B68" t="str">
-        <v>48024 View | Edit | Add opening stock | Delete</v>
+        <v>48024</v>
       </c>
       <c r="C68" t="str">
         <v>SANDIA SIN SEMILLA PZ</v>
@@ -2376,7 +2376,7 @@
         <v>1250</v>
       </c>
       <c r="B69" t="str">
-        <v>48241 View | Edit | Add opening stock | Delete</v>
+        <v>48241</v>
       </c>
       <c r="C69" t="str">
         <v>SANDIA PERSONAL PZ</v>
@@ -2405,7 +2405,7 @@
         <v>1249</v>
       </c>
       <c r="B70" t="str">
-        <v>53080 View | Edit | Add opening stock | Delete</v>
+        <v>53080</v>
       </c>
       <c r="C70" t="str">
         <v>SANDIA PERSONAL KG</v>
@@ -2434,7 +2434,7 @@
         <v>1248</v>
       </c>
       <c r="B71" t="str">
-        <v>47793 View | Edit | Add opening stock | Delete</v>
+        <v>47793</v>
       </c>
       <c r="C71" t="str">
         <v>SANDIA GDE PZ</v>
@@ -2463,7 +2463,7 @@
         <v>1247</v>
       </c>
       <c r="B72" t="str">
-        <v>60268 View | Edit | Add opening stock | Delete</v>
+        <v>60268</v>
       </c>
       <c r="C72" t="str">
         <v>SANDIA GDE KG</v>
@@ -2492,7 +2492,7 @@
         <v>1246</v>
       </c>
       <c r="B73" t="str">
-        <v>96675 View | Edit | Add opening stock | Delete</v>
+        <v>96675</v>
       </c>
       <c r="C73" t="str">
         <v>SALVO LIQUIDO</v>
@@ -2521,7 +2521,7 @@
         <v>1245</v>
       </c>
       <c r="B74" t="str">
-        <v>71199 View | Edit | Add opening stock | Delete</v>
+        <v>71199</v>
       </c>
       <c r="C74" t="str">
         <v>SALSA VALENTINA PORC</v>
@@ -2550,7 +2550,7 @@
         <v>1244</v>
       </c>
       <c r="B75" t="str">
-        <v>24952 View | Edit | Add opening stock | Delete</v>
+        <v>24952</v>
       </c>
       <c r="C75" t="str">
         <v>SALSA VALENTINA CH</v>
@@ -2579,7 +2579,7 @@
         <v>1243</v>
       </c>
       <c r="B76" t="str">
-        <v>56818 View | Edit | Add opening stock | Delete</v>
+        <v>56818</v>
       </c>
       <c r="C76" t="str">
         <v>SALSA VALENTINA 370ML</v>
@@ -2608,7 +2608,7 @@
         <v>1242</v>
       </c>
       <c r="B77" t="str">
-        <v>86885 View | Edit | Add opening stock | Delete</v>
+        <v>86885</v>
       </c>
       <c r="C77" t="str">
         <v>SALSA VALENTINA</v>
@@ -2637,7 +2637,7 @@
         <v>1241</v>
       </c>
       <c r="B78" t="str">
-        <v>79108 View | Edit | Add opening stock | Delete</v>
+        <v>79108</v>
       </c>
       <c r="C78" t="str">
         <v>SALSA TERIYAKI</v>
@@ -2666,7 +2666,7 @@
         <v>1240</v>
       </c>
       <c r="B79" t="str">
-        <v>56207 View | Edit | Add opening stock | Delete</v>
+        <v>56207</v>
       </c>
       <c r="C79" t="str">
         <v>SALSA TABASCO</v>
@@ -2695,7 +2695,7 @@
         <v>1239</v>
       </c>
       <c r="B80" t="str">
-        <v>71588 View | Edit | Add opening stock | Delete</v>
+        <v>71588</v>
       </c>
       <c r="C80" t="str">
         <v>SALSA SOYA KIKKOMAN 1.89</v>
@@ -2724,7 +2724,7 @@
         <v>1237</v>
       </c>
       <c r="B81" t="str">
-        <v>18383 View | Edit | Add opening stock | Delete</v>
+        <v>18383</v>
       </c>
       <c r="C81" t="str">
         <v>SALSA MAGGI LITRO</v>
@@ -2753,7 +2753,7 @@
         <v>1236</v>
       </c>
       <c r="B82" t="str">
-        <v>50532 View | Edit | Add opening stock | Delete</v>
+        <v>50532</v>
       </c>
       <c r="C82" t="str">
         <v>SALSA MAGGI 800ML</v>
@@ -2782,7 +2782,7 @@
         <v>1235</v>
       </c>
       <c r="B83" t="str">
-        <v>65261 View | Edit | Add opening stock | Delete</v>
+        <v>65261</v>
       </c>
       <c r="C83" t="str">
         <v>SALSA MAGGI 1.9Litro</v>
@@ -2811,7 +2811,7 @@
         <v>1232</v>
       </c>
       <c r="B84" t="str">
-        <v>24239 View | Edit | Add opening stock | Delete</v>
+        <v>24239</v>
       </c>
       <c r="C84" t="str">
         <v>SALSA HUICHOL Galón</v>
@@ -2840,7 +2840,7 @@
         <v>1230</v>
       </c>
       <c r="B85" t="str">
-        <v>53398 View | Edit | Add opening stock | Delete</v>
+        <v>53398</v>
       </c>
       <c r="C85" t="str">
         <v>SALSA GUACAMAYA</v>
@@ -2869,7 +2869,7 @@
         <v>1229</v>
       </c>
       <c r="B86" t="str">
-        <v>75783 View | Edit | Add opening stock | Delete</v>
+        <v>75783</v>
       </c>
       <c r="C86" t="str">
         <v>SALSA COSTA BRAVA 1Litro</v>
@@ -2898,7 +2898,7 @@
         <v>1227</v>
       </c>
       <c r="B87" t="str">
-        <v>17310 View | Edit | Add opening stock | Delete</v>
+        <v>17310</v>
       </c>
       <c r="C87" t="str">
         <v>SALSA CHAMOY 1.5Litro</v>
@@ -2927,7 +2927,7 @@
         <v>1226</v>
       </c>
       <c r="B88" t="str">
-        <v>18362 View | Edit | Add opening stock | Delete</v>
+        <v>18362</v>
       </c>
       <c r="C88" t="str">
         <v>SALSA CHAMOY</v>
@@ -2956,7 +2956,7 @@
         <v>1225</v>
       </c>
       <c r="B89" t="str">
-        <v>22823 View | Edit | Add opening stock | Delete</v>
+        <v>22823</v>
       </c>
       <c r="C89" t="str">
         <v>SALSA CATSUP POR</v>
@@ -2985,7 +2985,7 @@
         <v>1211</v>
       </c>
       <c r="B90" t="str">
-        <v>24944 View | Edit | Add opening stock | Delete</v>
+        <v>24944</v>
       </c>
       <c r="C90" t="str">
         <v>SAL GRANO KG</v>
@@ -3014,7 +3014,7 @@
         <v>1210</v>
       </c>
       <c r="B91" t="str">
-        <v>60571 View | Edit | Add opening stock | Delete</v>
+        <v>60571</v>
       </c>
       <c r="C91" t="str">
         <v>SAL GRANO BTO 3K</v>
@@ -3043,7 +3043,7 @@
         <v>1209</v>
       </c>
       <c r="B92" t="str">
-        <v>42078 View | Edit | Add opening stock | Delete</v>
+        <v>42078</v>
       </c>
       <c r="C92" t="str">
         <v>SAL FINA BOTE NO USAR</v>
@@ -3072,7 +3072,7 @@
         <v>1202</v>
       </c>
       <c r="B93" t="str">
-        <v>59519 View | Edit | Add opening stock | Delete</v>
+        <v>59519</v>
       </c>
       <c r="C93" t="str">
         <v>SAL COLIMA Paquete 1K</v>
@@ -3101,7 +3101,7 @@
         <v>1200</v>
       </c>
       <c r="B94" t="str">
-        <v>27901 View | Edit | Add opening stock | Delete</v>
+        <v>27901</v>
       </c>
       <c r="C94" t="str">
         <v>SACUDIDIOR</v>
@@ -3130,7 +3130,7 @@
         <v>1198</v>
       </c>
       <c r="B95" t="str">
-        <v>62650 View | Edit | Add opening stock | Delete</v>
+        <v>62650</v>
       </c>
       <c r="C95" t="str">
         <v>SABILA</v>
@@ -3159,7 +3159,7 @@
         <v>1197</v>
       </c>
       <c r="B96" t="str">
-        <v>96572 View | Edit | Add opening stock | Delete</v>
+        <v>96572</v>
       </c>
       <c r="C96" t="str">
         <v>ROYAL GDE 494 GRS</v>
@@ -3188,7 +3188,7 @@
         <v>1195</v>
       </c>
       <c r="B97" t="str">
-        <v>58777 View | Edit | Add opening stock | Delete</v>
+        <v>58777</v>
       </c>
       <c r="C97" t="str">
         <v>ROLLO MALLA</v>
@@ -3217,7 +3217,7 @@
         <v>1194</v>
       </c>
       <c r="B98" t="str">
-        <v>23390 View | Edit | Add opening stock | Delete</v>
+        <v>23390</v>
       </c>
       <c r="C98" t="str">
         <v>RICE CAKES QUINOA</v>
@@ -3246,7 +3246,7 @@
         <v>1193</v>
       </c>
       <c r="B99" t="str">
-        <v>91090 View | Edit | Add opening stock | Delete</v>
+        <v>91090</v>
       </c>
       <c r="C99" t="str">
         <v>REVOLitroURA P/PAJARO</v>
@@ -3275,7 +3275,7 @@
         <v>1189</v>
       </c>
       <c r="B100" t="str">
-        <v>91769 View | Edit | Add opening stock | Delete</v>
+        <v>91769</v>
       </c>
       <c r="C100" t="str">
         <v>RAID CASA Y JARDIN</v>
@@ -3304,7 +3304,7 @@
         <v>1184</v>
       </c>
       <c r="B101" t="str">
-        <v>80188 View | Edit | Add opening stock | Delete</v>
+        <v>80188</v>
       </c>
       <c r="C101" t="str">
         <v>QUESO1</v>
@@ -3333,7 +3333,7 @@
         <v>1183</v>
       </c>
       <c r="B102" t="str">
-        <v>45415 View | Edit | Add opening stock | Delete</v>
+        <v>45415</v>
       </c>
       <c r="C102" t="str">
         <v>QUESO RICOTA</v>
@@ -3362,7 +3362,7 @@
         <v>1180</v>
       </c>
       <c r="B103" t="str">
-        <v>58373 View | Edit | Add opening stock | Delete</v>
+        <v>58373</v>
       </c>
       <c r="C103" t="str">
         <v>QUESO PARMESAN</v>
@@ -3391,7 +3391,7 @@
         <v>1178</v>
       </c>
       <c r="B104" t="str">
-        <v>15845 View | Edit | Add opening stock | Delete</v>
+        <v>15845</v>
       </c>
       <c r="C104" t="str">
         <v>QUESO OAXACA</v>
@@ -3420,7 +3420,7 @@
         <v>1177</v>
       </c>
       <c r="B105" t="str">
-        <v>14133 View | Edit | Add opening stock | Delete</v>
+        <v>14133</v>
       </c>
       <c r="C105" t="str">
         <v>QUESO MOZARELLA RAY</v>
@@ -3449,7 +3449,7 @@
         <v>1175</v>
       </c>
       <c r="B106" t="str">
-        <v>25267 View | Edit | Add opening stock | Delete</v>
+        <v>25267</v>
       </c>
       <c r="C106" t="str">
         <v>QUESO MASCARPONE</v>
@@ -3478,7 +3478,7 @@
         <v>1173</v>
       </c>
       <c r="B107" t="str">
-        <v>25950 View | Edit | Add opening stock | Delete</v>
+        <v>25950</v>
       </c>
       <c r="C107" t="str">
         <v>QUESO DOBLE CREMA</v>
@@ -3507,7 +3507,7 @@
         <v>1172</v>
       </c>
       <c r="B108" t="str">
-        <v>88148 View | Edit | Add opening stock | Delete</v>
+        <v>88148</v>
       </c>
       <c r="C108" t="str">
         <v>QUESO DE MESA</v>
@@ -3536,7 +3536,7 @@
         <v>1169</v>
       </c>
       <c r="B109" t="str">
-        <v>63577 View | Edit | Add opening stock | Delete</v>
+        <v>63577</v>
       </c>
       <c r="C109" t="str">
         <v>QUESO COTAGGE</v>
@@ -3565,7 +3565,7 @@
         <v>1165</v>
       </c>
       <c r="B110" t="str">
-        <v>39201 View | Edit | Add opening stock | Delete</v>
+        <v>39201</v>
       </c>
       <c r="C110" t="str">
         <v>QUESO AMARILLO PQ</v>
@@ -3594,7 +3594,7 @@
         <v>1164</v>
       </c>
       <c r="B111" t="str">
-        <v>32695 View | Edit | Add opening stock | Delete</v>
+        <v>32695</v>
       </c>
       <c r="C111" t="str">
         <v>Q ADOBERA NAVARRO</v>
@@ -3623,7 +3623,7 @@
         <v>1159</v>
       </c>
       <c r="B112" t="str">
-        <v>58753 View | Edit | Add opening stock | Delete</v>
+        <v>58753</v>
       </c>
       <c r="C112" t="str">
         <v>POBLANO PZ</v>
@@ -3652,7 +3652,7 @@
         <v>1156</v>
       </c>
       <c r="B113" t="str">
-        <v>55086 View | Edit | Add opening stock | Delete</v>
+        <v>55086</v>
       </c>
       <c r="C113" t="str">
         <v>PLATANO TABASCO VDE PZA</v>
@@ -3681,7 +3681,7 @@
         <v>1155</v>
       </c>
       <c r="B114" t="str">
-        <v>37635 View | Edit | Add opening stock | Delete</v>
+        <v>37635</v>
       </c>
       <c r="C114" t="str">
         <v>PLATANO TABASCO VDE KG</v>
@@ -3710,7 +3710,7 @@
         <v>1154</v>
       </c>
       <c r="B115" t="str">
-        <v>40353 View | Edit | Add opening stock | Delete</v>
+        <v>40353</v>
       </c>
       <c r="C115" t="str">
         <v>PLATANO TABASCO VDE CJ</v>
@@ -3739,7 +3739,7 @@
         <v>1153</v>
       </c>
       <c r="B116" t="str">
-        <v>72284 View | Edit | Add opening stock | Delete</v>
+        <v>72284</v>
       </c>
       <c r="C116" t="str">
         <v>PLATANO TABASCO PUNTAS CJ</v>
@@ -3768,7 +3768,7 @@
         <v>1152</v>
       </c>
       <c r="B117" t="str">
-        <v>77301 View | Edit | Add opening stock | Delete</v>
+        <v>77301</v>
       </c>
       <c r="C117" t="str">
         <v>PLATANO TABASCO MADURO PZ</v>
@@ -3797,7 +3797,7 @@
         <v>1151</v>
       </c>
       <c r="B118" t="str">
-        <v>58171 View | Edit | Add opening stock | Delete</v>
+        <v>58171</v>
       </c>
       <c r="C118" t="str">
         <v>PLATANO TABASCO MADURO KG</v>
@@ -3826,7 +3826,7 @@
         <v>1150</v>
       </c>
       <c r="B119" t="str">
-        <v>86530 View | Edit | Add opening stock | Delete</v>
+        <v>86530</v>
       </c>
       <c r="C119" t="str">
         <v>PLATANO TABASCO MADURO CJ</v>
@@ -3855,7 +3855,7 @@
         <v>1149</v>
       </c>
       <c r="B120" t="str">
-        <v>51962 View | Edit | Add opening stock | Delete</v>
+        <v>51962</v>
       </c>
       <c r="C120" t="str">
         <v>PLATANO MACHO VDE PZA</v>
@@ -3884,7 +3884,7 @@
         <v>1148</v>
       </c>
       <c r="B121" t="str">
-        <v>12620 View | Edit | Add opening stock | Delete</v>
+        <v>12620</v>
       </c>
       <c r="C121" t="str">
         <v>PLATANO MACHO VDE KG</v>
@@ -3913,7 +3913,7 @@
         <v>1147</v>
       </c>
       <c r="B122" t="str">
-        <v>92475 View | Edit | Add opening stock | Delete</v>
+        <v>92475</v>
       </c>
       <c r="C122" t="str">
         <v>PLATANO MACHO MADURO PZ</v>
@@ -3942,7 +3942,7 @@
         <v>1143</v>
       </c>
       <c r="B123" t="str">
-        <v>73729 View | Edit | Add opening stock | Delete</v>
+        <v>73729</v>
       </c>
       <c r="C123" t="str">
         <v>PIÑON BLANCO</v>
@@ -3971,7 +3971,7 @@
         <v>1142</v>
       </c>
       <c r="B124" t="str">
-        <v>43309 View | Edit | Add opening stock | Delete</v>
+        <v>43309</v>
       </c>
       <c r="C124" t="str">
         <v>PIÑA MIEL VDE PZ</v>
@@ -4000,7 +4000,7 @@
         <v>1141</v>
       </c>
       <c r="B125" t="str">
-        <v>88166 View | Edit | Add opening stock | Delete</v>
+        <v>88166</v>
       </c>
       <c r="C125" t="str">
         <v>PIÑA MIEL VDE KG</v>
@@ -4029,7 +4029,7 @@
         <v>1140</v>
       </c>
       <c r="B126" t="str">
-        <v>67312 View | Edit | Add opening stock | Delete</v>
+        <v>67312</v>
       </c>
       <c r="C126" t="str">
         <v>PIÑA MIEL MAD PZ</v>
@@ -4058,7 +4058,7 @@
         <v>1139</v>
       </c>
       <c r="B127" t="str">
-        <v>47332 View | Edit | Add opening stock | Delete</v>
+        <v>47332</v>
       </c>
       <c r="C127" t="str">
         <v>PIÑA MIEL MAD KG</v>
@@ -4087,7 +4087,7 @@
         <v>1138</v>
       </c>
       <c r="B128" t="str">
-        <v>71141 View | Edit | Add opening stock | Delete</v>
+        <v>71141</v>
       </c>
       <c r="C128" t="str">
         <v>PIÑA CAYENA VERDE</v>
@@ -4116,7 +4116,7 @@
         <v>1131</v>
       </c>
       <c r="B129" t="str">
-        <v>78506 View | Edit | Add opening stock | Delete</v>
+        <v>78506</v>
       </c>
       <c r="C129" t="str">
         <v>PIMIENTA MOLIDA</v>
@@ -4145,7 +4145,7 @@
         <v>1129</v>
       </c>
       <c r="B130" t="str">
-        <v>83649 View | Edit | Add opening stock | Delete</v>
+        <v>83649</v>
       </c>
       <c r="C130" t="str">
         <v>PIMIENTA CAYENA MOLIDA</v>
@@ -4174,7 +4174,7 @@
         <v>1128</v>
       </c>
       <c r="B131" t="str">
-        <v>60590 View | Edit | Add opening stock | Delete</v>
+        <v>60590</v>
       </c>
       <c r="C131" t="str">
         <v>PIMIENTA CAYENA</v>
@@ -4203,7 +4203,7 @@
         <v>1124</v>
       </c>
       <c r="B132" t="str">
-        <v>12363 View | Edit | Add opening stock | Delete</v>
+        <v>12363</v>
       </c>
       <c r="C132" t="str">
         <v>PILONCILLO MORENO</v>
@@ -4232,7 +4232,7 @@
         <v>1118</v>
       </c>
       <c r="B133" t="str">
-        <v>90251 View | Edit | Add opening stock | Delete</v>
+        <v>90251</v>
       </c>
       <c r="C133" t="str">
         <v>PERUANO BOLA</v>
@@ -4261,7 +4261,7 @@
         <v>1112</v>
       </c>
       <c r="B134" t="str">
-        <v>21017 View | Edit | Add opening stock | Delete</v>
+        <v>21017</v>
       </c>
       <c r="C134" t="str">
         <v>PEPPERONI</v>
@@ -4290,7 +4290,7 @@
         <v>1111</v>
       </c>
       <c r="B135" t="str">
-        <v>85205 View | Edit | Add opening stock | Delete</v>
+        <v>85205</v>
       </c>
       <c r="C135" t="str">
         <v>PEPITA DE CALABAZA</v>
@@ -4319,7 +4319,7 @@
         <v>1110</v>
       </c>
       <c r="B136" t="str">
-        <v>14843 View | Edit | Add opening stock | Delete</v>
+        <v>14843</v>
       </c>
       <c r="C136" t="str">
         <v>PEPINO GDE PZ</v>
@@ -4348,7 +4348,7 @@
         <v>1109</v>
       </c>
       <c r="B137" t="str">
-        <v>35141 View | Edit | Add opening stock | Delete</v>
+        <v>35141</v>
       </c>
       <c r="C137" t="str">
         <v>PEPINO GDE KG</v>
@@ -4377,7 +4377,7 @@
         <v>1107</v>
       </c>
       <c r="B138" t="str">
-        <v>46308 View | Edit | Add opening stock | Delete</v>
+        <v>46308</v>
       </c>
       <c r="C138" t="str">
         <v>PEPINO CH PZ</v>
@@ -4406,7 +4406,7 @@
         <v>1106</v>
       </c>
       <c r="B139" t="str">
-        <v>92108 View | Edit | Add opening stock | Delete</v>
+        <v>92108</v>
       </c>
       <c r="C139" t="str">
         <v>PEPINO CH KG</v>
@@ -4435,7 +4435,7 @@
         <v>1105</v>
       </c>
       <c r="B140" t="str">
-        <v>83921 View | Edit | Add opening stock | Delete</v>
+        <v>83921</v>
       </c>
       <c r="C140" t="str">
         <v>PEPINO BABY PZ</v>
@@ -4464,7 +4464,7 @@
         <v>1104</v>
       </c>
       <c r="B141" t="str">
-        <v>37244 View | Edit | Add opening stock | Delete</v>
+        <v>37244</v>
       </c>
       <c r="C141" t="str">
         <v>PEPINO BABY KG</v>
@@ -4493,7 +4493,7 @@
         <v>1103</v>
       </c>
       <c r="B142" t="str">
-        <v>18942 View | Edit | Add opening stock | Delete</v>
+        <v>18942</v>
       </c>
       <c r="C142" t="str">
         <v>PEPINO BABY CJ</v>
@@ -4522,7 +4522,7 @@
         <v>1102</v>
       </c>
       <c r="B143" t="str">
-        <v>90380 View | Edit | Add opening stock | Delete</v>
+        <v>90380</v>
       </c>
       <c r="C143" t="str">
         <v>PEPINO AME PZ</v>
@@ -4551,7 +4551,7 @@
         <v>1101</v>
       </c>
       <c r="B144" t="str">
-        <v>93921 View | Edit | Add opening stock | Delete</v>
+        <v>93921</v>
       </c>
       <c r="C144" t="str">
         <v>PEPINILLO REBANADO 3.7</v>
@@ -4580,7 +4580,7 @@
         <v>1100</v>
       </c>
       <c r="B145" t="str">
-        <v>41655 View | Edit | Add opening stock | Delete</v>
+        <v>41655</v>
       </c>
       <c r="C145" t="str">
         <v>PEPINILLO</v>
@@ -4609,7 +4609,7 @@
         <v>1099</v>
       </c>
       <c r="B146" t="str">
-        <v>73863 View | Edit | Add opening stock | Delete</v>
+        <v>73863</v>
       </c>
       <c r="C146" t="str">
         <v>PEPIAN ESPECIAL</v>
@@ -4638,7 +4638,7 @@
         <v>1097</v>
       </c>
       <c r="B147" t="str">
-        <v>59179 View | Edit | Add opening stock | Delete</v>
+        <v>59179</v>
       </c>
       <c r="C147" t="str">
         <v>PEÑAFIEL MINERAL LATA 355ML</v>
@@ -4667,7 +4667,7 @@
         <v>1092</v>
       </c>
       <c r="B148" t="str">
-        <v>21192 View | Edit | Add opening stock | Delete</v>
+        <v>21192</v>
       </c>
       <c r="C148" t="str">
         <v>PASTILLAS MICHELSON</v>
@@ -4696,7 +4696,7 @@
         <v>1089</v>
       </c>
       <c r="B149" t="str">
-        <v>16360 View | Edit | Add opening stock | Delete</v>
+        <v>16360</v>
       </c>
       <c r="C149" t="str">
         <v>PASTA PQTE</v>
@@ -4725,7 +4725,7 @@
         <v>1087</v>
       </c>
       <c r="B150" t="str">
-        <v>80789 View | Edit | Add opening stock | Delete</v>
+        <v>80789</v>
       </c>
       <c r="C150" t="str">
         <v>PASTA MIZU</v>
@@ -4754,7 +4754,7 @@
         <v>1085</v>
       </c>
       <c r="B151" t="str">
-        <v>54663 View | Edit | Add opening stock | Delete</v>
+        <v>54663</v>
       </c>
       <c r="C151" t="str">
         <v>PASTA CODITO/PQTE</v>
@@ -4783,7 +4783,7 @@
         <v>1080</v>
       </c>
       <c r="B152" t="str">
-        <v>36546 View | Edit | Add opening stock | Delete</v>
+        <v>36546</v>
       </c>
       <c r="C152" t="str">
         <v>PAPAYA VDE PZ</v>
@@ -4812,7 +4812,7 @@
         <v>1079</v>
       </c>
       <c r="B153" t="str">
-        <v>95165 View | Edit | Add opening stock | Delete</v>
+        <v>95165</v>
       </c>
       <c r="C153" t="str">
         <v>PAPAYA VDE KG</v>
@@ -4841,7 +4841,7 @@
         <v>1078</v>
       </c>
       <c r="B154" t="str">
-        <v>50056 View | Edit | Add opening stock | Delete</v>
+        <v>50056</v>
       </c>
       <c r="C154" t="str">
         <v>PAPAYA VDE CJ</v>
@@ -4870,7 +4870,7 @@
         <v>1077</v>
       </c>
       <c r="B155" t="str">
-        <v>70954 View | Edit | Add opening stock | Delete</v>
+        <v>70954</v>
       </c>
       <c r="C155" t="str">
         <v>PAPAYA MAD PZ</v>
@@ -4899,7 +4899,7 @@
         <v>1076</v>
       </c>
       <c r="B156" t="str">
-        <v>52450 View | Edit | Add opening stock | Delete</v>
+        <v>52450</v>
       </c>
       <c r="C156" t="str">
         <v>PAPAYA MAD KG</v>
@@ -4928,7 +4928,7 @@
         <v>1073</v>
       </c>
       <c r="B157" t="str">
-        <v>94593 View | Edit | Add opening stock | Delete</v>
+        <v>94593</v>
       </c>
       <c r="C157" t="str">
         <v>PAPA P/DORAR EXTRA KG</v>
@@ -4957,7 +4957,7 @@
         <v>1072</v>
       </c>
       <c r="B158" t="str">
-        <v>23220 View | Edit | Add opening stock | Delete</v>
+        <v>23220</v>
       </c>
       <c r="C158" t="str">
         <v>PAPA FRANCESA</v>
@@ -4986,7 +4986,7 @@
         <v>1071</v>
       </c>
       <c r="B159" t="str">
-        <v>26760 View | Edit | Add opening stock | Delete</v>
+        <v>26760</v>
       </c>
       <c r="C159" t="str">
         <v>PAPA CAMB BLANCA PZ</v>
@@ -5015,7 +5015,7 @@
         <v>1070</v>
       </c>
       <c r="B160" t="str">
-        <v>54782 View | Edit | Add opening stock | Delete</v>
+        <v>54782</v>
       </c>
       <c r="C160" t="str">
         <v>PAPA CAMB BLANCA KG</v>
@@ -5044,7 +5044,7 @@
         <v>1068</v>
       </c>
       <c r="B161" t="str">
-        <v>92723 View | Edit | Add opening stock | Delete</v>
+        <v>92723</v>
       </c>
       <c r="C161" t="str">
         <v>PAPA 2A BLANCA PZ</v>
@@ -5073,7 +5073,7 @@
         <v>1067</v>
       </c>
       <c r="B162" t="str">
-        <v>43430 View | Edit | Add opening stock | Delete</v>
+        <v>43430</v>
       </c>
       <c r="C162" t="str">
         <v>PAPA 2A BLANCA KG</v>
@@ -5102,7 +5102,7 @@
         <v>1066</v>
       </c>
       <c r="B163" t="str">
-        <v>44620 View | Edit | Add opening stock | Delete</v>
+        <v>44620</v>
       </c>
       <c r="C163" t="str">
         <v>PAPA 1A BLANCA PZ</v>
@@ -5131,7 +5131,7 @@
         <v>1065</v>
       </c>
       <c r="B164" t="str">
-        <v>10610 View | Edit | Add opening stock | Delete</v>
+        <v>10610</v>
       </c>
       <c r="C164" t="str">
         <v>PAPA 1A BLANCA KG</v>
@@ -5160,7 +5160,7 @@
         <v>1064</v>
       </c>
       <c r="B165" t="str">
-        <v>92364 View | Edit | Add opening stock | Delete</v>
+        <v>92364</v>
       </c>
       <c r="C165" t="str">
         <v>PAPA 1A AMARILLA KG</v>
@@ -5189,7 +5189,7 @@
         <v>1061</v>
       </c>
       <c r="B166" t="str">
-        <v>60770 View | Edit | Add opening stock | Delete</v>
+        <v>60770</v>
       </c>
       <c r="C166" t="str">
         <v>PANELA LALA 400GR</v>
@@ -5218,7 +5218,7 @@
         <v>1057</v>
       </c>
       <c r="B167" t="str">
-        <v>21199 View | Edit | Add opening stock | Delete</v>
+        <v>21199</v>
       </c>
       <c r="C167" t="str">
         <v>PAN PARRILLERO P/HAMBUERGUESA</v>
@@ -5247,7 +5247,7 @@
         <v>1056</v>
       </c>
       <c r="B168" t="str">
-        <v>30093 View | Edit | Add opening stock | Delete</v>
+        <v>30093</v>
       </c>
       <c r="C168" t="str">
         <v>PAN PARA HOT DOG</v>
@@ -5276,7 +5276,7 @@
         <v>1055</v>
       </c>
       <c r="B169" t="str">
-        <v>21985 View | Edit | Add opening stock | Delete</v>
+        <v>21985</v>
       </c>
       <c r="C169" t="str">
         <v>PAN P/HAMBURGUESA</v>
@@ -5305,7 +5305,7 @@
         <v>1053</v>
       </c>
       <c r="B170" t="str">
-        <v>42754 View | Edit | Add opening stock | Delete</v>
+        <v>42754</v>
       </c>
       <c r="C170" t="str">
         <v>PAN BIMBO INTEGRAL</v>
@@ -5334,7 +5334,7 @@
         <v>1046</v>
       </c>
       <c r="B171" t="str">
-        <v>57440 View | Edit | Add opening stock | Delete</v>
+        <v>57440</v>
       </c>
       <c r="C171" t="str">
         <v>PALITOS P/BROCHETA</v>
@@ -5363,7 +5363,7 @@
         <v>1043</v>
       </c>
       <c r="B172" t="str">
-        <v>34804 View | Edit | Add opening stock | Delete</v>
+        <v>34804</v>
       </c>
       <c r="C172" t="str">
         <v>PALETA SANDIBROCHA</v>
@@ -5392,7 +5392,7 @@
         <v>1039</v>
       </c>
       <c r="B173" t="str">
-        <v>59895 View | Edit | Add opening stock | Delete</v>
+        <v>59895</v>
       </c>
       <c r="C173" t="str">
         <v>NUGEETS</v>
@@ -5421,7 +5421,7 @@
         <v>1037</v>
       </c>
       <c r="B174" t="str">
-        <v>57405 View | Edit | Add opening stock | Delete</v>
+        <v>57405</v>
       </c>
       <c r="C174" t="str">
         <v>NUEZ MOSCADA MOLIDA</v>
@@ -5450,7 +5450,7 @@
         <v>1023</v>
       </c>
       <c r="B175" t="str">
-        <v>31022 View | Edit | Add opening stock | Delete</v>
+        <v>31022</v>
       </c>
       <c r="C175" t="str">
         <v>NEGRA MOD</v>
@@ -5479,7 +5479,7 @@
         <v>1021</v>
       </c>
       <c r="B176" t="str">
-        <v>15703 View | Edit | Add opening stock | Delete</v>
+        <v>15703</v>
       </c>
       <c r="C176" t="str">
         <v>NARANJADA DE CITRICOS DEL VALLE 600ML</v>
@@ -5508,7 +5508,7 @@
         <v>1020</v>
       </c>
       <c r="B177" t="str">
-        <v>62127 View | Edit | Add opening stock | Delete</v>
+        <v>62127</v>
       </c>
       <c r="C177" t="str">
         <v>NARANJA PZ</v>
@@ -5537,7 +5537,7 @@
         <v>1019</v>
       </c>
       <c r="B178" t="str">
-        <v>40177 View | Edit | Add opening stock | Delete</v>
+        <v>40177</v>
       </c>
       <c r="C178" t="str">
         <v>NACHOS JALAPE?O GDE</v>
@@ -5566,7 +5566,7 @@
         <v>1018</v>
       </c>
       <c r="B179" t="str">
-        <v>46813 View | Edit | Add opening stock | Delete</v>
+        <v>46813</v>
       </c>
       <c r="C179" t="str">
         <v>NACHOS CAREY BOLSA 3KG</v>
@@ -5595,7 +5595,7 @@
         <v>1016</v>
       </c>
       <c r="B180" t="str">
-        <v>67388 View | Edit | Add opening stock | Delete</v>
+        <v>67388</v>
       </c>
       <c r="C180" t="str">
         <v>NABO LEÑA PZ</v>
@@ -5624,7 +5624,7 @@
         <v>1015</v>
       </c>
       <c r="B181" t="str">
-        <v>28247 View | Edit | Add opening stock | Delete</v>
+        <v>28247</v>
       </c>
       <c r="C181" t="str">
         <v>MOSTAZA PORCION</v>
@@ -5653,7 +5653,7 @@
         <v>1014</v>
       </c>
       <c r="B182" t="str">
-        <v>11532 View | Edit | Add opening stock | Delete</v>
+        <v>11532</v>
       </c>
       <c r="C182" t="str">
         <v>MOSTAZA MCCORMICK D 430GR</v>
@@ -5682,7 +5682,7 @@
         <v>1010</v>
       </c>
       <c r="B183" t="str">
-        <v>88547 View | Edit | Add opening stock | Delete</v>
+        <v>88547</v>
       </c>
       <c r="C183" t="str">
         <v>MORRON VERDE PZ</v>
@@ -5711,7 +5711,7 @@
         <v>1009</v>
       </c>
       <c r="B184" t="str">
-        <v>88700 View | Edit | Add opening stock | Delete</v>
+        <v>88700</v>
       </c>
       <c r="C184" t="str">
         <v>MORRON VERDE KG</v>
@@ -5740,7 +5740,7 @@
         <v>1008</v>
       </c>
       <c r="B185" t="str">
-        <v>58025 View | Edit | Add opening stock | Delete</v>
+        <v>58025</v>
       </c>
       <c r="C185" t="str">
         <v>MORRON ROJO PZ</v>
@@ -5769,7 +5769,7 @@
         <v>1007</v>
       </c>
       <c r="B186" t="str">
-        <v>27472 View | Edit | Add opening stock | Delete</v>
+        <v>27472</v>
       </c>
       <c r="C186" t="str">
         <v>MORRON ROJO KG</v>
@@ -5798,7 +5798,7 @@
         <v>1006</v>
       </c>
       <c r="B187" t="str">
-        <v>64589 View | Edit | Add opening stock | Delete</v>
+        <v>64589</v>
       </c>
       <c r="C187" t="str">
         <v>MORRON ROJO CJ CH</v>
@@ -5827,7 +5827,7 @@
         <v>1004</v>
       </c>
       <c r="B188" t="str">
-        <v>95917 View | Edit | Add opening stock | Delete</v>
+        <v>95917</v>
       </c>
       <c r="C188" t="str">
         <v>MORRON NARANJA PZ</v>
@@ -5856,7 +5856,7 @@
         <v>1003</v>
       </c>
       <c r="B189" t="str">
-        <v>23171 View | Edit | Add opening stock | Delete</v>
+        <v>23171</v>
       </c>
       <c r="C189" t="str">
         <v>MORRON NARANJA</v>
@@ -5885,7 +5885,7 @@
         <v>1002</v>
       </c>
       <c r="B190" t="str">
-        <v>53539 View | Edit | Add opening stock | Delete</v>
+        <v>53539</v>
       </c>
       <c r="C190" t="str">
         <v>MORRON AMARILLO PZA</v>
@@ -5914,7 +5914,7 @@
         <v>1001</v>
       </c>
       <c r="B191" t="str">
-        <v>41196 View | Edit | Add opening stock | Delete</v>
+        <v>41196</v>
       </c>
       <c r="C191" t="str">
         <v>MORRON AMARILLO KG</v>
@@ -5943,7 +5943,7 @@
         <v>999</v>
       </c>
       <c r="B192" t="str">
-        <v>13016 View | Edit | Add opening stock | Delete</v>
+        <v>13016</v>
       </c>
       <c r="C192" t="str">
         <v>MOLIDA MIXTA</v>
@@ -5972,7 +5972,7 @@
         <v>993</v>
       </c>
       <c r="B193" t="str">
-        <v>39487 View | Edit | Add opening stock | Delete</v>
+        <v>39487</v>
       </c>
       <c r="C193" t="str">
         <v>MEZCLA DE LA CASA</v>
@@ -6001,7 +6001,7 @@
         <v>991</v>
       </c>
       <c r="B194" t="str">
-        <v>90267 View | Edit | Add opening stock | Delete</v>
+        <v>90267</v>
       </c>
       <c r="C194" t="str">
         <v>MEZCLA CALIFORNIA</v>
@@ -6030,7 +6030,7 @@
         <v>979</v>
       </c>
       <c r="B195" t="str">
-        <v>55401 View | Edit | Add opening stock | Delete</v>
+        <v>55401</v>
       </c>
       <c r="C195" t="str">
         <v>MAZAPAN SIN AZUCAR</v>
@@ -6059,7 +6059,7 @@
         <v>978</v>
       </c>
       <c r="B196" t="str">
-        <v>58224 View | Edit | Add opening stock | Delete</v>
+        <v>58224</v>
       </c>
       <c r="C196" t="str">
         <v>MAYONESA PORCION</v>
@@ -6088,7 +6088,7 @@
         <v>977</v>
       </c>
       <c r="B197" t="str">
-        <v>68465 View | Edit | Add opening stock | Delete</v>
+        <v>68465</v>
       </c>
       <c r="C197" t="str">
         <v>MAYONESA GDE</v>
@@ -6117,7 +6117,7 @@
         <v>976</v>
       </c>
       <c r="B198" t="str">
-        <v>92263 View | Edit | Add opening stock | Delete</v>
+        <v>92263</v>
       </c>
       <c r="C198" t="str">
         <v>MAYONESA FCO</v>
@@ -6146,7 +6146,7 @@
         <v>969</v>
       </c>
       <c r="B199" t="str">
-        <v>71906 View | Edit | Add opening stock | Delete</v>
+        <v>71906</v>
       </c>
       <c r="C199" t="str">
         <v>MARGARINA PZ</v>
@@ -6175,7 +6175,7 @@
         <v>966</v>
       </c>
       <c r="B200" t="str">
-        <v>45750 View | Edit | Add opening stock | Delete</v>
+        <v>45750</v>
       </c>
       <c r="C200" t="str">
         <v>MANZANA VERDE PZ</v>
@@ -6204,7 +6204,7 @@
         <v>965</v>
       </c>
       <c r="B201" t="str">
-        <v>59770 View | Edit | Add opening stock | Delete</v>
+        <v>59770</v>
       </c>
       <c r="C201" t="str">
         <v>MANZANA VERDE KG</v>
@@ -6233,7 +6233,7 @@
         <v>964</v>
       </c>
       <c r="B202" t="str">
-        <v>28295 View | Edit | Add opening stock | Delete</v>
+        <v>28295</v>
       </c>
       <c r="C202" t="str">
         <v>MANZANA VERDE CJ</v>
@@ -6262,7 +6262,7 @@
         <v>963</v>
       </c>
       <c r="B203" t="str">
-        <v>59776 View | Edit | Add opening stock | Delete</v>
+        <v>59776</v>
       </c>
       <c r="C203" t="str">
         <v>MANZANA ROJA PZ</v>
@@ -6291,7 +6291,7 @@
         <v>962</v>
       </c>
       <c r="B204" t="str">
-        <v>34699 View | Edit | Add opening stock | Delete</v>
+        <v>34699</v>
       </c>
       <c r="C204" t="str">
         <v>MANZANA ROJA KG</v>
@@ -6320,7 +6320,7 @@
         <v>956</v>
       </c>
       <c r="B205" t="str">
-        <v>50125 View | Edit | Add opening stock | Delete</v>
+        <v>50125</v>
       </c>
       <c r="C205" t="str">
         <v>MANTEQUILLA FLEX ROJA</v>
@@ -6349,7 +6349,7 @@
         <v>955</v>
       </c>
       <c r="B206" t="str">
-        <v>90803 View | Edit | Add opening stock | Delete</v>
+        <v>90803</v>
       </c>
       <c r="C206" t="str">
         <v>MANTEQUILLA EUGENIA</v>
@@ -6378,7 +6378,7 @@
         <v>953</v>
       </c>
       <c r="B207" t="str">
-        <v>18739 View | Edit | Add opening stock | Delete</v>
+        <v>18739</v>
       </c>
       <c r="C207" t="str">
         <v>MANTECA KG</v>
@@ -6407,7 +6407,7 @@
         <v>952</v>
       </c>
       <c r="B208" t="str">
-        <v>83331 View | Edit | Add opening stock | Delete</v>
+        <v>83331</v>
       </c>
       <c r="C208" t="str">
         <v>MANTECA CUBETA 3KG</v>
@@ -6436,7 +6436,7 @@
         <v>949</v>
       </c>
       <c r="B209" t="str">
-        <v>38776 View | Edit | Add opening stock | Delete</v>
+        <v>38776</v>
       </c>
       <c r="C209" t="str">
         <v>MANGO VDE PZ</v>
@@ -6465,7 +6465,7 @@
         <v>948</v>
       </c>
       <c r="B210" t="str">
-        <v>68285 View | Edit | Add opening stock | Delete</v>
+        <v>68285</v>
       </c>
       <c r="C210" t="str">
         <v>MANGO VDE KG</v>
@@ -6494,7 +6494,7 @@
         <v>947</v>
       </c>
       <c r="B211" t="str">
-        <v>14301 View | Edit | Add opening stock | Delete</v>
+        <v>14301</v>
       </c>
       <c r="C211" t="str">
         <v>MANGO MAD PZ</v>
@@ -6523,7 +6523,7 @@
         <v>946</v>
       </c>
       <c r="B212" t="str">
-        <v>98773 View | Edit | Add opening stock | Delete</v>
+        <v>98773</v>
       </c>
       <c r="C212" t="str">
         <v>MANGO MAD KG</v>
@@ -6552,7 +6552,7 @@
         <v>945</v>
       </c>
       <c r="B213" t="str">
-        <v>61979 View | Edit | Add opening stock | Delete</v>
+        <v>61979</v>
       </c>
       <c r="C213" t="str">
         <v>MANGO CONGELADO BOTE</v>
@@ -6581,7 +6581,7 @@
         <v>933</v>
       </c>
       <c r="B214" t="str">
-        <v>33240 View | Edit | Add opening stock | Delete</v>
+        <v>33240</v>
       </c>
       <c r="C214" t="str">
         <v>LIMON S/S PZ</v>
@@ -6610,7 +6610,7 @@
         <v>932</v>
       </c>
       <c r="B215" t="str">
-        <v>59925 View | Edit | Add opening stock | Delete</v>
+        <v>59925</v>
       </c>
       <c r="C215" t="str">
         <v>LIMON S/S KG</v>
@@ -6639,7 +6639,7 @@
         <v>931</v>
       </c>
       <c r="B216" t="str">
-        <v>22045 View | Edit | Add opening stock | Delete</v>
+        <v>22045</v>
       </c>
       <c r="C216" t="str">
         <v>LIMON REAL PZ</v>
@@ -6668,7 +6668,7 @@
         <v>930</v>
       </c>
       <c r="B217" t="str">
-        <v>25981 View | Edit | Add opening stock | Delete</v>
+        <v>25981</v>
       </c>
       <c r="C217" t="str">
         <v>LIMON REAL KG</v>
@@ -6697,7 +6697,7 @@
         <v>929</v>
       </c>
       <c r="B218" t="str">
-        <v>86279 View | Edit | Add opening stock | Delete</v>
+        <v>86279</v>
       </c>
       <c r="C218" t="str">
         <v>LIMON REAL CJ</v>
@@ -6726,7 +6726,7 @@
         <v>928</v>
       </c>
       <c r="B219" t="str">
-        <v>20791 View | Edit | Add opening stock | Delete</v>
+        <v>20791</v>
       </c>
       <c r="C219" t="str">
         <v>LIMON C/S KG</v>
@@ -6755,7 +6755,7 @@
         <v>920</v>
       </c>
       <c r="B220" t="str">
-        <v>81483 View | Edit | Add opening stock | Delete</v>
+        <v>81483</v>
       </c>
       <c r="C220" t="str">
         <v>LECHUGA ROMANA CJ</v>
@@ -6784,7 +6784,7 @@
         <v>919</v>
       </c>
       <c r="B221" t="str">
-        <v>94738 View | Edit | Add opening stock | Delete</v>
+        <v>94738</v>
       </c>
       <c r="C221" t="str">
         <v>LECHUGA RADIQUIO</v>
@@ -6813,7 +6813,7 @@
         <v>918</v>
       </c>
       <c r="B222" t="str">
-        <v>37318 View | Edit | Add opening stock | Delete</v>
+        <v>37318</v>
       </c>
       <c r="C222" t="str">
         <v>LECHUGA LARGA CJ</v>
@@ -6842,7 +6842,7 @@
         <v>909</v>
       </c>
       <c r="B223" t="str">
-        <v>48988 View | Edit | Add opening stock | Delete</v>
+        <v>48988</v>
       </c>
       <c r="C223" t="str">
         <v>LECHE SANTA CLARA Litro</v>
@@ -6871,7 +6871,7 @@
         <v>906</v>
       </c>
       <c r="B224" t="str">
-        <v>56655 View | Edit | Add opening stock | Delete</v>
+        <v>56655</v>
       </c>
       <c r="C224" t="str">
         <v>LECHE DESLACTOSADA LALA</v>
@@ -6900,7 +6900,7 @@
         <v>905</v>
       </c>
       <c r="B225" t="str">
-        <v>55683 View | Edit | Add opening stock | Delete</v>
+        <v>55683</v>
       </c>
       <c r="C225" t="str">
         <v>LECHE DESLAC LIGTH LALA</v>
@@ -6929,7 +6929,7 @@
         <v>904</v>
       </c>
       <c r="B226" t="str">
-        <v>59426 View | Edit | Add opening stock | Delete</v>
+        <v>59426</v>
       </c>
       <c r="C226" t="str">
         <v>LECHE DESLAC</v>
@@ -6958,7 +6958,7 @@
         <v>903</v>
       </c>
       <c r="B227" t="str">
-        <v>59870 View | Edit | Add opening stock | Delete</v>
+        <v>59870</v>
       </c>
       <c r="C227" t="str">
         <v>LECHE CLAVEL LITRO</v>
@@ -6987,7 +6987,7 @@
         <v>902</v>
       </c>
       <c r="B228" t="str">
-        <v>20819 View | Edit | Add opening stock | Delete</v>
+        <v>20819</v>
       </c>
       <c r="C228" t="str">
         <v>LECHE CLAVEL 360ML</v>
@@ -7016,7 +7016,7 @@
         <v>900</v>
       </c>
       <c r="B229" t="str">
-        <v>13631 View | Edit | Add opening stock | Delete</v>
+        <v>13631</v>
       </c>
       <c r="C229" t="str">
         <v>LECHE ALMENDRA ADES</v>
@@ -7045,7 +7045,7 @@
         <v>893</v>
       </c>
       <c r="B230" t="str">
-        <v>99820 View | Edit | Add opening stock | Delete</v>
+        <v>99820</v>
       </c>
       <c r="C230" t="str">
         <v>JUMEX DE PIÑA</v>
@@ -7074,7 +7074,7 @@
         <v>892</v>
       </c>
       <c r="B231" t="str">
-        <v>92634 View | Edit | Add opening stock | Delete</v>
+        <v>92634</v>
       </c>
       <c r="C231" t="str">
         <v>JUGO ZANAHORIA NAT</v>
@@ -7103,7 +7103,7 @@
         <v>889</v>
       </c>
       <c r="B232" t="str">
-        <v>87000 View | Edit | Add opening stock | Delete</v>
+        <v>87000</v>
       </c>
       <c r="C232" t="str">
         <v>JUGO NARANJA CarteraON</v>
@@ -7132,7 +7132,7 @@
         <v>886</v>
       </c>
       <c r="B233" t="str">
-        <v>71894 View | Edit | Add opening stock | Delete</v>
+        <v>71894</v>
       </c>
       <c r="C233" t="str">
         <v>JUGO CarteraON</v>
@@ -7161,7 +7161,7 @@
         <v>883</v>
       </c>
       <c r="B234" t="str">
-        <v>26331 View | Edit | Add opening stock | Delete</v>
+        <v>26331</v>
       </c>
       <c r="C234" t="str">
         <v>JITOMATE SALADET 3A ROJO KG</v>
@@ -7190,7 +7190,7 @@
         <v>882</v>
       </c>
       <c r="B235" t="str">
-        <v>67136 View | Edit | Add opening stock | Delete</v>
+        <v>67136</v>
       </c>
       <c r="C235" t="str">
         <v>JITOMATE SALADET 3A ROJO CJ</v>
@@ -7219,7 +7219,7 @@
         <v>881</v>
       </c>
       <c r="B236" t="str">
-        <v>25920 View | Edit | Add opening stock | Delete</v>
+        <v>25920</v>
       </c>
       <c r="C236" t="str">
         <v>JITOMATE SALADET 3A RAY CJ</v>
@@ -7248,7 +7248,7 @@
         <v>880</v>
       </c>
       <c r="B237" t="str">
-        <v>68159 View | Edit | Add opening stock | Delete</v>
+        <v>68159</v>
       </c>
       <c r="C237" t="str">
         <v>JITOMATE SALADET 2A ROJO PZ</v>
@@ -7277,7 +7277,7 @@
         <v>879</v>
       </c>
       <c r="B238" t="str">
-        <v>82799 View | Edit | Add opening stock | Delete</v>
+        <v>82799</v>
       </c>
       <c r="C238" t="str">
         <v>JITOMATE SALADET 2A KG</v>
@@ -7306,7 +7306,7 @@
         <v>878</v>
       </c>
       <c r="B239" t="str">
-        <v>46637 View | Edit | Add opening stock | Delete</v>
+        <v>46637</v>
       </c>
       <c r="C239" t="str">
         <v>JITOMATE SALADET 2A CJ</v>
@@ -7335,7 +7335,7 @@
         <v>877</v>
       </c>
       <c r="B240" t="str">
-        <v>84855 View | Edit | Add opening stock | Delete</v>
+        <v>84855</v>
       </c>
       <c r="C240" t="str">
         <v>JITOMATE SALADET 1A ROJO PZ</v>
@@ -7364,7 +7364,7 @@
         <v>876</v>
       </c>
       <c r="B241" t="str">
-        <v>85698 View | Edit | Add opening stock | Delete</v>
+        <v>85698</v>
       </c>
       <c r="C241" t="str">
         <v>JITOMATE SALADET 1A ROJO KG</v>
@@ -7393,7 +7393,7 @@
         <v>875</v>
       </c>
       <c r="B242" t="str">
-        <v>34832 View | Edit | Add opening stock | Delete</v>
+        <v>34832</v>
       </c>
       <c r="C242" t="str">
         <v>JITOMATE SALADET 1A ROJO CJ</v>
@@ -7422,7 +7422,7 @@
         <v>874</v>
       </c>
       <c r="B243" t="str">
-        <v>70413 View | Edit | Add opening stock | Delete</v>
+        <v>70413</v>
       </c>
       <c r="C243" t="str">
         <v>JITOMATE SALADET 1A RAY PZ</v>
@@ -7451,7 +7451,7 @@
         <v>873</v>
       </c>
       <c r="B244" t="str">
-        <v>63169 View | Edit | Add opening stock | Delete</v>
+        <v>63169</v>
       </c>
       <c r="C244" t="str">
         <v>JITOMATE SALADET 1A RAY KG</v>
@@ -7480,7 +7480,7 @@
         <v>872</v>
       </c>
       <c r="B245" t="str">
-        <v>11241 View | Edit | Add opening stock | Delete</v>
+        <v>11241</v>
       </c>
       <c r="C245" t="str">
         <v>JITOMATE SALADET 1A RAY CJ</v>
@@ -7509,7 +7509,7 @@
         <v>870</v>
       </c>
       <c r="B246" t="str">
-        <v>98404 View | Edit | Add opening stock | Delete</v>
+        <v>98404</v>
       </c>
       <c r="C246" t="str">
         <v>JITOMATE BOLA VDE PZ</v>
@@ -7538,7 +7538,7 @@
         <v>869</v>
       </c>
       <c r="B247" t="str">
-        <v>91339 View | Edit | Add opening stock | Delete</v>
+        <v>91339</v>
       </c>
       <c r="C247" t="str">
         <v>JITOMATE BOLA VDE KG</v>
@@ -7567,7 +7567,7 @@
         <v>868</v>
       </c>
       <c r="B248" t="str">
-        <v>31760 View | Edit | Add opening stock | Delete</v>
+        <v>31760</v>
       </c>
       <c r="C248" t="str">
         <v>JITOMATE BOLA VDE CJ</v>
@@ -7596,7 +7596,7 @@
         <v>867</v>
       </c>
       <c r="B249" t="str">
-        <v>32889 View | Edit | Add opening stock | Delete</v>
+        <v>32889</v>
       </c>
       <c r="C249" t="str">
         <v>JITOMATE BOLA ROJO PZ</v>
@@ -7625,7 +7625,7 @@
         <v>866</v>
       </c>
       <c r="B250" t="str">
-        <v>98246 View | Edit | Add opening stock | Delete</v>
+        <v>98246</v>
       </c>
       <c r="C250" t="str">
         <v>JITOMATE BOLA ROJO KG</v>
@@ -7654,7 +7654,7 @@
         <v>865</v>
       </c>
       <c r="B251" t="str">
-        <v>57458 View | Edit | Add opening stock | Delete</v>
+        <v>57458</v>
       </c>
       <c r="C251" t="str">
         <v>JITOMATE BOLA ROJO CJ</v>
@@ -7683,7 +7683,7 @@
         <v>864</v>
       </c>
       <c r="B252" t="str">
-        <v>54087 View | Edit | Add opening stock | Delete</v>
+        <v>54087</v>
       </c>
       <c r="C252" t="str">
         <v>JITOMATE BOLA RAY PZ</v>
@@ -7712,7 +7712,7 @@
         <v>863</v>
       </c>
       <c r="B253" t="str">
-        <v>14442 View | Edit | Add opening stock | Delete</v>
+        <v>14442</v>
       </c>
       <c r="C253" t="str">
         <v>JITOMATE BOLA RAY KG</v>
@@ -7741,7 +7741,7 @@
         <v>861</v>
       </c>
       <c r="B254" t="str">
-        <v>45257 View | Edit | Add opening stock | Delete</v>
+        <v>45257</v>
       </c>
       <c r="C254" t="str">
         <v>JENGIBRE PZ</v>
@@ -7770,7 +7770,7 @@
         <v>860</v>
       </c>
       <c r="B255" t="str">
-        <v>64449 View | Edit | Add opening stock | Delete</v>
+        <v>64449</v>
       </c>
       <c r="C255" t="str">
         <v>JARRA</v>
@@ -7799,7 +7799,7 @@
         <v>858</v>
       </c>
       <c r="B256" t="str">
-        <v>81015 View | Edit | Add opening stock | Delete</v>
+        <v>81015</v>
       </c>
       <c r="C256" t="str">
         <v>JAMON SERRANO</v>
@@ -7828,7 +7828,7 @@
         <v>857</v>
       </c>
       <c r="B257" t="str">
-        <v>91989 View | Edit | Add opening stock | Delete</v>
+        <v>91989</v>
       </c>
       <c r="C257" t="str">
         <v>JAMON DE PIERNA CORONA</v>
@@ -7857,7 +7857,7 @@
         <v>856</v>
       </c>
       <c r="B258" t="str">
-        <v>24780 View | Edit | Add opening stock | Delete</v>
+        <v>24780</v>
       </c>
       <c r="C258" t="str">
         <v>JAMON ANDALUCIA PIERNA</v>
@@ -7886,7 +7886,7 @@
         <v>844</v>
       </c>
       <c r="B259" t="str">
-        <v>21210 View | Edit | Add opening stock | Delete</v>
+        <v>21210</v>
       </c>
       <c r="C259" t="str">
         <v>JABON LIQUIDO ROSA VENUS 500ML</v>
@@ -7915,7 +7915,7 @@
         <v>843</v>
       </c>
       <c r="B260" t="str">
-        <v>32459 View | Edit | Add opening stock | Delete</v>
+        <v>32459</v>
       </c>
       <c r="C260" t="str">
         <v>JABON LIQUIDO</v>
@@ -7944,7 +7944,7 @@
         <v>842</v>
       </c>
       <c r="B261" t="str">
-        <v>53970 View | Edit | Add opening stock | Delete</v>
+        <v>53970</v>
       </c>
       <c r="C261" t="str">
         <v>ITALIANA EVA</v>
@@ -7973,7 +7973,7 @@
         <v>841</v>
       </c>
       <c r="B262" t="str">
-        <v>81832 View | Edit | Add opening stock | Delete</v>
+        <v>81832</v>
       </c>
       <c r="C262" t="str">
         <v>ISADORA PERUANO</v>
@@ -8002,7 +8002,7 @@
         <v>840</v>
       </c>
       <c r="B263" t="str">
-        <v>86545 View | Edit | Add opening stock | Delete</v>
+        <v>86545</v>
       </c>
       <c r="C263" t="str">
         <v>HUNGARO</v>
@@ -8031,7 +8031,7 @@
         <v>838</v>
       </c>
       <c r="B264" t="str">
-        <v>29370 View | Edit | Add opening stock | Delete</v>
+        <v>29370</v>
       </c>
       <c r="C264" t="str">
         <v>HUITLACOCHE Cartera</v>
@@ -8060,7 +8060,7 @@
         <v>832</v>
       </c>
       <c r="B265" t="str">
-        <v>73015 View | Edit | Add opening stock | Delete</v>
+        <v>73015</v>
       </c>
       <c r="C265" t="str">
         <v>HOJA D ESTEVIA PQ</v>
@@ -8089,7 +8089,7 @@
         <v>816</v>
       </c>
       <c r="B266" t="str">
-        <v>28356 View | Edit | Add opening stock | Delete</v>
+        <v>28356</v>
       </c>
       <c r="C266" t="str">
         <v>GRANOS ANCESTRALES</v>
@@ -8118,7 +8118,7 @@
         <v>813</v>
       </c>
       <c r="B267" t="str">
-        <v>26529 View | Edit | Add opening stock | Delete</v>
+        <v>26529</v>
       </c>
       <c r="C267" t="str">
         <v>GRANADA DESG</v>
@@ -8147,7 +8147,7 @@
         <v>811</v>
       </c>
       <c r="B268" t="str">
-        <v>14375 View | Edit | Add opening stock | Delete</v>
+        <v>14375</v>
       </c>
       <c r="C268" t="str">
         <v>GOMA XANTANA</v>
@@ -8176,7 +8176,7 @@
         <v>804</v>
       </c>
       <c r="B269" t="str">
-        <v>64781 View | Edit | Add opening stock | Delete</v>
+        <v>64781</v>
       </c>
       <c r="C269" t="str">
         <v>GALLETAS VARIAS</v>
@@ -8205,7 +8205,7 @@
         <v>801</v>
       </c>
       <c r="B270" t="str">
-        <v>70761 View | Edit | Add opening stock | Delete</v>
+        <v>70761</v>
       </c>
       <c r="C270" t="str">
         <v>GALLETA SALADA CJ</v>
@@ -8234,7 +8234,7 @@
         <v>800</v>
       </c>
       <c r="B271" t="str">
-        <v>23877 View | Edit | Add opening stock | Delete</v>
+        <v>23877</v>
       </c>
       <c r="C271" t="str">
         <v>GALLETA SALADA 186GR</v>
@@ -8263,7 +8263,7 @@
         <v>799</v>
       </c>
       <c r="B272" t="str">
-        <v>59879 View | Edit | Add opening stock | Delete</v>
+        <v>59879</v>
       </c>
       <c r="C272" t="str">
         <v>GALLETA PEKE PAKES</v>
@@ -8292,7 +8292,7 @@
         <v>798</v>
       </c>
       <c r="B273" t="str">
-        <v>56741 View | Edit | Add opening stock | Delete</v>
+        <v>56741</v>
       </c>
       <c r="C273" t="str">
         <v>GALLETA OREO SIN RELLENO KG</v>
@@ -8321,7 +8321,7 @@
         <v>792</v>
       </c>
       <c r="B274" t="str">
-        <v>58604 View | Edit | Add opening stock | Delete</v>
+        <v>58604</v>
       </c>
       <c r="C274" t="str">
         <v>FRIJOLES PQ</v>
@@ -8350,7 +8350,7 @@
         <v>791</v>
       </c>
       <c r="B275" t="str">
-        <v>41436 View | Edit | Add opening stock | Delete</v>
+        <v>41436</v>
       </c>
       <c r="C275" t="str">
         <v>FRIJOL TEXANO</v>
@@ -8379,7 +8379,7 @@
         <v>789</v>
       </c>
       <c r="B276" t="str">
-        <v>82017 View | Edit | Add opening stock | Delete</v>
+        <v>82017</v>
       </c>
       <c r="C276" t="str">
         <v>FRIJOL PERUANO HIGERA KG</v>
@@ -8408,7 +8408,7 @@
         <v>788</v>
       </c>
       <c r="B277" t="str">
-        <v>28711 View | Edit | Add opening stock | Delete</v>
+        <v>28711</v>
       </c>
       <c r="C277" t="str">
         <v>FRIJOL PERUANO HIGERA PaqueteTO</v>
@@ -8437,7 +8437,7 @@
         <v>786</v>
       </c>
       <c r="B278" t="str">
-        <v>46273 View | Edit | Add opening stock | Delete</v>
+        <v>46273</v>
       </c>
       <c r="C278" t="str">
         <v>FRIJOL FLOR DE JUNIO</v>
@@ -8466,7 +8466,7 @@
         <v>782</v>
       </c>
       <c r="B279" t="str">
-        <v>54574 View | Edit | Add opening stock | Delete</v>
+        <v>54574</v>
       </c>
       <c r="C279" t="str">
         <v>FRESA KG</v>
@@ -8495,7 +8495,7 @@
         <v>780</v>
       </c>
       <c r="B280" t="str">
-        <v>41707 View | Edit | Add opening stock | Delete</v>
+        <v>41707</v>
       </c>
       <c r="C280" t="str">
         <v>FRANCESA EVA</v>
@@ -8524,7 +8524,7 @@
         <v>776</v>
       </c>
       <c r="B281" t="str">
-        <v>47550 View | Edit | Add opening stock | Delete</v>
+        <v>47550</v>
       </c>
       <c r="C281" t="str">
         <v>FLAN PQ</v>
@@ -8553,7 +8553,7 @@
         <v>772</v>
       </c>
       <c r="B282" t="str">
-        <v>95562 View | Edit | Add opening stock | Delete</v>
+        <v>95562</v>
       </c>
       <c r="C282" t="str">
         <v>FILETE PESCADO</v>
@@ -8582,7 +8582,7 @@
         <v>769</v>
       </c>
       <c r="B283" t="str">
-        <v>81988 View | Edit | Add opening stock | Delete</v>
+        <v>81988</v>
       </c>
       <c r="C283" t="str">
         <v>F-DIAZ FRESA</v>
@@ -8611,7 +8611,7 @@
         <v>767</v>
       </c>
       <c r="B284" t="str">
-        <v>12463 View | Edit | Add opening stock | Delete</v>
+        <v>12463</v>
       </c>
       <c r="C284" t="str">
         <v>FALDA RES P/DESHEBRAR</v>
@@ -8640,7 +8640,7 @@
         <v>766</v>
       </c>
       <c r="B285" t="str">
-        <v>28167 View | Edit | Add opening stock | Delete</v>
+        <v>28167</v>
       </c>
       <c r="C285" t="str">
         <v>FAPaqueteOSO CAJA</v>
@@ -8669,7 +8669,7 @@
         <v>765</v>
       </c>
       <c r="B286" t="str">
-        <v>98643 View | Edit | Add opening stock | Delete</v>
+        <v>98643</v>
       </c>
       <c r="C286" t="str">
         <v>F DIAZ MANGO</v>
@@ -8698,7 +8698,7 @@
         <v>759</v>
       </c>
       <c r="B287" t="str">
-        <v>31229 View | Edit | Add opening stock | Delete</v>
+        <v>31229</v>
       </c>
       <c r="C287" t="str">
         <v>ESPARRAGO JUMBO</v>
@@ -8727,7 +8727,7 @@
         <v>758</v>
       </c>
       <c r="B288" t="str">
-        <v>86337 View | Edit | Add opening stock | Delete</v>
+        <v>86337</v>
       </c>
       <c r="C288" t="str">
         <v>ESPARRAGO ESTANDAR</v>
@@ -8756,7 +8756,7 @@
         <v>757</v>
       </c>
       <c r="B289" t="str">
-        <v>68485 View | Edit | Add opening stock | Delete</v>
+        <v>68485</v>
       </c>
       <c r="C289" t="str">
         <v>ENSALADA VERDURA LATA</v>
@@ -8785,7 +8785,7 @@
         <v>748</v>
       </c>
       <c r="B290" t="str">
-        <v>65544 View | Edit | Add opening stock | Delete</v>
+        <v>65544</v>
       </c>
       <c r="C290" t="str">
         <v>DULCES VARIOS</v>
@@ -8814,7 +8814,7 @@
         <v>745</v>
       </c>
       <c r="B291" t="str">
-        <v>33282 View | Edit | Add opening stock | Delete</v>
+        <v>33282</v>
       </c>
       <c r="C291" t="str">
         <v>DETERGENTE MAS COLOR</v>
@@ -8843,7 +8843,7 @@
         <v>743</v>
       </c>
       <c r="B292" t="str">
-        <v>31061 View | Edit | Add opening stock | Delete</v>
+        <v>31061</v>
       </c>
       <c r="C292" t="str">
         <v>DEMIGLASE</v>
@@ -8872,7 +8872,7 @@
         <v>740</v>
       </c>
       <c r="B293" t="str">
-        <v>42479 View | Edit | Add opening stock | Delete</v>
+        <v>42479</v>
       </c>
       <c r="C293" t="str">
         <v>CURCUMA</v>
@@ -8901,7 +8901,7 @@
         <v>735</v>
       </c>
       <c r="B294" t="str">
-        <v>28031 View | Edit | Add opening stock | Delete</v>
+        <v>28031</v>
       </c>
       <c r="C294" t="str">
         <v>CREMA SELLO ROJO RANCHERA Litro</v>
@@ -8930,7 +8930,7 @@
         <v>734</v>
       </c>
       <c r="B295" t="str">
-        <v>87401 View | Edit | Add opening stock | Delete</v>
+        <v>87401</v>
       </c>
       <c r="C295" t="str">
         <v>CREMA SELLO ROJO RANCHERA 1/2Litro</v>
@@ -8959,7 +8959,7 @@
         <v>733</v>
       </c>
       <c r="B296" t="str">
-        <v>91984 View | Edit | Add opening stock | Delete</v>
+        <v>91984</v>
       </c>
       <c r="C296" t="str">
         <v>CREMA SANDRITA</v>
@@ -8988,7 +8988,7 @@
         <v>732</v>
       </c>
       <c r="B297" t="str">
-        <v>32811 View | Edit | Add opening stock | Delete</v>
+        <v>32811</v>
       </c>
       <c r="C297" t="str">
         <v>CREMA PZ</v>
@@ -9017,7 +9017,7 @@
         <v>719</v>
       </c>
       <c r="B298" t="str">
-        <v>21639 View | Edit | Add opening stock | Delete</v>
+        <v>21639</v>
       </c>
       <c r="C298" t="str">
         <v>CONT DE 1/2LitroO</v>
@@ -9046,7 +9046,7 @@
         <v>717</v>
       </c>
       <c r="B299" t="str">
-        <v>48023 View | Edit | Add opening stock | Delete</v>
+        <v>48023</v>
       </c>
       <c r="C299" t="str">
         <v>CONT 6 X 6</v>
@@ -9075,7 +9075,7 @@
         <v>713</v>
       </c>
       <c r="B300" t="str">
-        <v>72037 View | Edit | Add opening stock | Delete</v>
+        <v>72037</v>
       </c>
       <c r="C300" t="str">
         <v>CONDIMENTO</v>
@@ -9104,7 +9104,7 @@
         <v>712</v>
       </c>
       <c r="B301" t="str">
-        <v>68978 View | Edit | Add opening stock | Delete</v>
+        <v>68978</v>
       </c>
       <c r="C301" t="str">
         <v>CONCENTRADO YUKA FRESA</v>
@@ -9133,7 +9133,7 @@
         <v>711</v>
       </c>
       <c r="B302" t="str">
-        <v>25001 View | Edit | Add opening stock | Delete</v>
+        <v>25001</v>
       </c>
       <c r="C302" t="str">
         <v>CONCENTRADO COCO</v>
@@ -9162,7 +9162,7 @@
         <v>707</v>
       </c>
       <c r="B303" t="str">
-        <v>10139 View | Edit | Add opening stock | Delete</v>
+        <v>10139</v>
       </c>
       <c r="C303" t="str">
         <v>COLORANTE AMARILLO</v>
@@ -9191,7 +9191,7 @@
         <v>705</v>
       </c>
       <c r="B304" t="str">
-        <v>62795 View | Edit | Add opening stock | Delete</v>
+        <v>62795</v>
       </c>
       <c r="C304" t="str">
         <v>COL MORADO PZ</v>
@@ -9220,7 +9220,7 @@
         <v>703</v>
       </c>
       <c r="B305" t="str">
-        <v>42560 View | Edit | Add opening stock | Delete</v>
+        <v>42560</v>
       </c>
       <c r="C305" t="str">
         <v>COL DE BRUSELAS</v>
@@ -9249,7 +9249,7 @@
         <v>702</v>
       </c>
       <c r="B306" t="str">
-        <v>24674 View | Edit | Add opening stock | Delete</v>
+        <v>24674</v>
       </c>
       <c r="C306" t="str">
         <v>COL BLANCO PZ</v>
@@ -9278,7 +9278,7 @@
         <v>697</v>
       </c>
       <c r="B307" t="str">
-        <v>88141 View | Edit | Add opening stock | Delete</v>
+        <v>88141</v>
       </c>
       <c r="C307" t="str">
         <v>COCA COLA SURTIDA LATA</v>
@@ -9307,7 +9307,7 @@
         <v>696</v>
       </c>
       <c r="B308" t="str">
-        <v>22703 View | Edit | Add opening stock | Delete</v>
+        <v>22703</v>
       </c>
       <c r="C308" t="str">
         <v>COCA COLA SIN AZUCAR LATA</v>
@@ -9336,7 +9336,7 @@
         <v>695</v>
       </c>
       <c r="B309" t="str">
-        <v>63387 View | Edit | Add opening stock | Delete</v>
+        <v>63387</v>
       </c>
       <c r="C309" t="str">
         <v>COCA COLA SIN AZUCAR LATA</v>
@@ -9365,7 +9365,7 @@
         <v>694</v>
       </c>
       <c r="B310" t="str">
-        <v>31258 View | Edit | Add opening stock | Delete</v>
+        <v>31258</v>
       </c>
       <c r="C310" t="str">
         <v>COCA COLA LIHGT PZ</v>
@@ -9394,7 +9394,7 @@
         <v>691</v>
       </c>
       <c r="B311" t="str">
-        <v>65992 View | Edit | Add opening stock | Delete</v>
+        <v>65992</v>
       </c>
       <c r="C311" t="str">
         <v>COCA COLA 2Litro</v>
@@ -9423,7 +9423,7 @@
         <v>690</v>
       </c>
       <c r="B312" t="str">
-        <v>44039 View | Edit | Add opening stock | Delete</v>
+        <v>44039</v>
       </c>
       <c r="C312" t="str">
         <v>COBERTURA DE CHOCOLATE</v>
@@ -9452,7 +9452,7 @@
         <v>689</v>
       </c>
       <c r="B313" t="str">
-        <v>57915 View | Edit | Add opening stock | Delete</v>
+        <v>57915</v>
       </c>
       <c r="C313" t="str">
         <v>COBERTURA CHOCOLATE 1Litro</v>
@@ -9481,7 +9481,7 @@
         <v>687</v>
       </c>
       <c r="B314" t="str">
-        <v>84289 View | Edit | Add opening stock | Delete</v>
+        <v>84289</v>
       </c>
       <c r="C314" t="str">
         <v>CLOR GEL</v>
@@ -9510,7 +9510,7 @@
         <v>682</v>
       </c>
       <c r="B315" t="str">
-        <v>39932 View | Edit | Add opening stock | Delete</v>
+        <v>39932</v>
       </c>
       <c r="C315" t="str">
         <v>CHULETA AHUMADA</v>
@@ -9539,7 +9539,7 @@
         <v>681</v>
       </c>
       <c r="B316" t="str">
-        <v>88860 View | Edit | Add opening stock | Delete</v>
+        <v>88860</v>
       </c>
       <c r="C316" t="str">
         <v>CHORIZO CORONA</v>
@@ -9568,7 +9568,7 @@
         <v>675</v>
       </c>
       <c r="B317" t="str">
-        <v>97256 View | Edit | Add opening stock | Delete</v>
+        <v>97256</v>
       </c>
       <c r="C317" t="str">
         <v>CHOCOLATE TURIN</v>
@@ -9597,7 +9597,7 @@
         <v>674</v>
       </c>
       <c r="B318" t="str">
-        <v>87033 View | Edit | Add opening stock | Delete</v>
+        <v>87033</v>
       </c>
       <c r="C318" t="str">
         <v>CHOCOLATE OBSCURO</v>
@@ -9626,7 +9626,7 @@
         <v>672</v>
       </c>
       <c r="B319" t="str">
-        <v>84895 View | Edit | Add opening stock | Delete</v>
+        <v>84895</v>
       </c>
       <c r="C319" t="str">
         <v>CHOCOLATE BOCADIN</v>
@@ -9655,7 +9655,7 @@
         <v>670</v>
       </c>
       <c r="B320" t="str">
-        <v>72907 View | Edit | Add opening stock | Delete</v>
+        <v>72907</v>
       </c>
       <c r="C320" t="str">
         <v>CHOCOLATE AMARGO TURIN</v>
@@ -9684,7 +9684,7 @@
         <v>668</v>
       </c>
       <c r="B321" t="str">
-        <v>33587 View | Edit | Add opening stock | Delete</v>
+        <v>33587</v>
       </c>
       <c r="C321" t="str">
         <v>CHOCOLATE ALPEZZI</v>
@@ -9713,7 +9713,7 @@
         <v>667</v>
       </c>
       <c r="B322" t="str">
-        <v>54284 View | Edit | Add opening stock | Delete</v>
+        <v>54284</v>
       </c>
       <c r="C322" t="str">
         <v>CHOCOLATE ABUELITA</v>
@@ -9742,7 +9742,7 @@
         <v>666</v>
       </c>
       <c r="B323" t="str">
-        <v>24372 View | Edit | Add opening stock | Delete</v>
+        <v>24372</v>
       </c>
       <c r="C323" t="str">
         <v>CHISPAS DE CHOCOLATE</v>
@@ -9771,7 +9771,7 @@
         <v>665</v>
       </c>
       <c r="B324" t="str">
-        <v>40817 View | Edit | Add opening stock | Delete</v>
+        <v>40817</v>
       </c>
       <c r="C324" t="str">
         <v>CHISPAS CHOCOLATE BLANCO</v>
@@ -9800,7 +9800,7 @@
         <v>663</v>
       </c>
       <c r="B325" t="str">
-        <v>33907 View | Edit | Add opening stock | Delete</v>
+        <v>33907</v>
       </c>
       <c r="C325" t="str">
         <v>CHIPOTLE LATA 220GR</v>
@@ -9829,7 +9829,7 @@
         <v>662</v>
       </c>
       <c r="B326" t="str">
-        <v>49563 View | Edit | Add opening stock | Delete</v>
+        <v>49563</v>
       </c>
       <c r="C326" t="str">
         <v>CHIPOTLE LATA 2.8</v>
@@ -9858,7 +9858,7 @@
         <v>661</v>
       </c>
       <c r="B327" t="str">
-        <v>78867 View | Edit | Add opening stock | Delete</v>
+        <v>78867</v>
       </c>
       <c r="C327" t="str">
         <v>CHINCHAYOTE PZ</v>
@@ -9887,7 +9887,7 @@
         <v>659</v>
       </c>
       <c r="B328" t="str">
-        <v>10972 View | Edit | Add opening stock | Delete</v>
+        <v>10972</v>
       </c>
       <c r="C328" t="str">
         <v>CHILitroEPIN</v>
@@ -9916,7 +9916,7 @@
         <v>657</v>
       </c>
       <c r="B329" t="str">
-        <v>45784 View | Edit | Add opening stock | Delete</v>
+        <v>45784</v>
       </c>
       <c r="C329" t="str">
         <v>CHILE SERRANO ROJO KG</v>
@@ -9945,7 +9945,7 @@
         <v>656</v>
       </c>
       <c r="B330" t="str">
-        <v>72345 View | Edit | Add opening stock | Delete</v>
+        <v>72345</v>
       </c>
       <c r="C330" t="str">
         <v>CHILE SERRANO PZ</v>
@@ -9974,7 +9974,7 @@
         <v>654</v>
       </c>
       <c r="B331" t="str">
-        <v>70700 View | Edit | Add opening stock | Delete</v>
+        <v>70700</v>
       </c>
       <c r="C331" t="str">
         <v>CHILE SERRANO DELGADO KG</v>
@@ -10003,7 +10003,7 @@
         <v>650</v>
       </c>
       <c r="B332" t="str">
-        <v>34837 View | Edit | Add opening stock | Delete</v>
+        <v>34837</v>
       </c>
       <c r="C332" t="str">
         <v>CHILE MANZANO PZ</v>
@@ -10032,7 +10032,7 @@
         <v>648</v>
       </c>
       <c r="B333" t="str">
-        <v>29713 View | Edit | Add opening stock | Delete</v>
+        <v>29713</v>
       </c>
       <c r="C333" t="str">
         <v>CHILE DE ARBOL YAHUALICA S/C</v>
@@ -10061,7 +10061,7 @@
         <v>646</v>
       </c>
       <c r="B334" t="str">
-        <v>72957 View | Edit | Add opening stock | Delete</v>
+        <v>72957</v>
       </c>
       <c r="C334" t="str">
         <v>CHILE ARBOL VDE</v>
@@ -10090,7 +10090,7 @@
         <v>645</v>
       </c>
       <c r="B335" t="str">
-        <v>20676 View | Edit | Add opening stock | Delete</v>
+        <v>20676</v>
       </c>
       <c r="C335" t="str">
         <v>CHILE ARBOL MOLIDO</v>
@@ -10119,7 +10119,7 @@
         <v>641</v>
       </c>
       <c r="B336" t="str">
-        <v>61143 View | Edit | Add opening stock | Delete</v>
+        <v>61143</v>
       </c>
       <c r="C336" t="str">
         <v>CHICHARO CONGELADO</v>
@@ -10148,7 +10148,7 @@
         <v>635</v>
       </c>
       <c r="B337" t="str">
-        <v>78751 View | Edit | Add opening stock | Delete</v>
+        <v>78751</v>
       </c>
       <c r="C337" t="str">
         <v>CHAMPIÑON PORTOBELLO</v>
@@ -10177,7 +10177,7 @@
         <v>634</v>
       </c>
       <c r="B338" t="str">
-        <v>82965 View | Edit | Add opening stock | Delete</v>
+        <v>82965</v>
       </c>
       <c r="C338" t="str">
         <v>CHAMPIÑON PORTOBELLO</v>
@@ -10206,7 +10206,7 @@
         <v>633</v>
       </c>
       <c r="B339" t="str">
-        <v>19426 View | Edit | Add opening stock | Delete</v>
+        <v>19426</v>
       </c>
       <c r="C339" t="str">
         <v>CHAMPIÑON CREMINI KG</v>
@@ -10235,7 +10235,7 @@
         <v>631</v>
       </c>
       <c r="B340" t="str">
-        <v>76933 View | Edit | Add opening stock | Delete</v>
+        <v>76933</v>
       </c>
       <c r="C340" t="str">
         <v>CHAMPIÑON BLANCO MEDIANO</v>
@@ -10264,7 +10264,7 @@
         <v>630</v>
       </c>
       <c r="B341" t="str">
-        <v>46083 View | Edit | Add opening stock | Delete</v>
+        <v>46083</v>
       </c>
       <c r="C341" t="str">
         <v>CHAMPIÑON BLANCO JUMBO</v>
@@ -10293,7 +10293,7 @@
         <v>627</v>
       </c>
       <c r="B342" t="str">
-        <v>81714 View | Edit | Add opening stock | Delete</v>
+        <v>81714</v>
       </c>
       <c r="C342" t="str">
         <v>CH PUYA</v>
@@ -10322,7 +10322,7 @@
         <v>626</v>
       </c>
       <c r="B343" t="str">
-        <v>86192 View | Edit | Add opening stock | Delete</v>
+        <v>86192</v>
       </c>
       <c r="C343" t="str">
         <v>CH MULATO</v>
@@ -10351,7 +10351,7 @@
         <v>625</v>
       </c>
       <c r="B344" t="str">
-        <v>96141 View | Edit | Add opening stock | Delete</v>
+        <v>96141</v>
       </c>
       <c r="C344" t="str">
         <v>CH JAPONES</v>
@@ -10380,7 +10380,7 @@
         <v>624</v>
       </c>
       <c r="B345" t="str">
-        <v>71400 View | Edit | Add opening stock | Delete</v>
+        <v>71400</v>
       </c>
       <c r="C345" t="str">
         <v>CH CHIPOTLE</v>
@@ -10409,7 +10409,7 @@
         <v>623</v>
       </c>
       <c r="B346" t="str">
-        <v>12770 View | Edit | Add opening stock | Delete</v>
+        <v>12770</v>
       </c>
       <c r="C346" t="str">
         <v>CH CHILACATE</v>
@@ -10438,7 +10438,7 @@
         <v>622</v>
       </c>
       <c r="B347" t="str">
-        <v>18103 View | Edit | Add opening stock | Delete</v>
+        <v>18103</v>
       </c>
       <c r="C347" t="str">
         <v>CH AMORTAJADO</v>
@@ -10467,7 +10467,7 @@
         <v>618</v>
       </c>
       <c r="B348" t="str">
-        <v>82756 View | Edit | Add opening stock | Delete</v>
+        <v>82756</v>
       </c>
       <c r="C348" t="str">
         <v>CEREAL/CAJA</v>
@@ -10496,7 +10496,7 @@
         <v>617</v>
       </c>
       <c r="B349" t="str">
-        <v>92432 View | Edit | Add opening stock | Delete</v>
+        <v>92432</v>
       </c>
       <c r="C349" t="str">
         <v>CEBOLLA TAQ</v>
@@ -10525,7 +10525,7 @@
         <v>616</v>
       </c>
       <c r="B350" t="str">
-        <v>52970 View | Edit | Add opening stock | Delete</v>
+        <v>52970</v>
       </c>
       <c r="C350" t="str">
         <v>CEBOLLA MORADA PZ</v>
@@ -10554,7 +10554,7 @@
         <v>615</v>
       </c>
       <c r="B351" t="str">
-        <v>34690 View | Edit | Add opening stock | Delete</v>
+        <v>34690</v>
       </c>
       <c r="C351" t="str">
         <v>CEBOLLA MORADA KG</v>
@@ -10583,7 +10583,7 @@
         <v>612</v>
       </c>
       <c r="B352" t="str">
-        <v>35976 View | Edit | Add opening stock | Delete</v>
+        <v>35976</v>
       </c>
       <c r="C352" t="str">
         <v>CEBOLLA BLANCA PZ</v>
@@ -10612,7 +10612,7 @@
         <v>611</v>
       </c>
       <c r="B353" t="str">
-        <v>26437 View | Edit | Add opening stock | Delete</v>
+        <v>26437</v>
       </c>
       <c r="C353" t="str">
         <v>CEBOLLA BLANCA KG</v>
@@ -10641,7 +10641,7 @@
         <v>610</v>
       </c>
       <c r="B354" t="str">
-        <v>63297 View | Edit | Add opening stock | Delete</v>
+        <v>63297</v>
       </c>
       <c r="C354" t="str">
         <v>CEBOLLA AMA</v>
@@ -10670,7 +10670,7 @@
         <v>606</v>
       </c>
       <c r="B355" t="str">
-        <v>97143 View | Edit | Add opening stock | Delete</v>
+        <v>97143</v>
       </c>
       <c r="C355" t="str">
         <v>CATSUP HEINZ PORCION</v>
@@ -10699,7 +10699,7 @@
         <v>603</v>
       </c>
       <c r="B356" t="str">
-        <v>82012 View | Edit | Add opening stock | Delete</v>
+        <v>82012</v>
       </c>
       <c r="C356" t="str">
         <v>CARNE MOLIDA CERDO</v>
@@ -10728,7 +10728,7 @@
         <v>594</v>
       </c>
       <c r="B357" t="str">
-        <v>31454 View | Edit | Add opening stock | Delete</v>
+        <v>31454</v>
       </c>
       <c r="C357" t="str">
         <v>CALORO PZ</v>
@@ -10757,7 +10757,7 @@
         <v>593</v>
       </c>
       <c r="B358" t="str">
-        <v>34210 View | Edit | Add opening stock | Delete</v>
+        <v>34210</v>
       </c>
       <c r="C358" t="str">
         <v>CALORO KG</v>
@@ -10786,7 +10786,7 @@
         <v>592</v>
       </c>
       <c r="B359" t="str">
-        <v>76497 View | Edit | Add opening stock | Delete</v>
+        <v>76497</v>
       </c>
       <c r="C359" t="str">
         <v>CALORO ESCABECHE</v>
@@ -10815,7 +10815,7 @@
         <v>591</v>
       </c>
       <c r="B360" t="str">
-        <v>10159 View | Edit | Add opening stock | Delete</v>
+        <v>10159</v>
       </c>
       <c r="C360" t="str">
         <v>CALORO CH KG</v>
@@ -10844,7 +10844,7 @@
         <v>590</v>
       </c>
       <c r="B361" t="str">
-        <v>14345 View | Edit | Add opening stock | Delete</v>
+        <v>14345</v>
       </c>
       <c r="C361" t="str">
         <v>CALIFORNIA PZ</v>
@@ -10873,7 +10873,7 @@
         <v>589</v>
       </c>
       <c r="B362" t="str">
-        <v>62906 View | Edit | Add opening stock | Delete</v>
+        <v>62906</v>
       </c>
       <c r="C362" t="str">
         <v>CALABAZA PZ</v>
@@ -10902,7 +10902,7 @@
         <v>588</v>
       </c>
       <c r="B363" t="str">
-        <v>12128 View | Edit | Add opening stock | Delete</v>
+        <v>12128</v>
       </c>
       <c r="C363" t="str">
         <v>CALABAZA KG</v>
@@ -10931,7 +10931,7 @@
         <v>586</v>
       </c>
       <c r="B364" t="str">
-        <v>19693 View | Edit | Add opening stock | Delete</v>
+        <v>19693</v>
       </c>
       <c r="C364" t="str">
         <v>CALABAZA CASTILLA</v>
@@ -10960,7 +10960,7 @@
         <v>585</v>
       </c>
       <c r="B365" t="str">
-        <v>44207 View | Edit | Add opening stock | Delete</v>
+        <v>44207</v>
       </c>
       <c r="C365" t="str">
         <v>CALABAZA BOLA PZ</v>
@@ -10989,7 +10989,7 @@
         <v>584</v>
       </c>
       <c r="B366" t="str">
-        <v>74958 View | Edit | Add opening stock | Delete</v>
+        <v>74958</v>
       </c>
       <c r="C366" t="str">
         <v>CAJETA DE MEMBRILLO</v>
@@ -11018,7 +11018,7 @@
         <v>582</v>
       </c>
       <c r="B367" t="str">
-        <v>81509 View | Edit | Add opening stock | Delete</v>
+        <v>81509</v>
       </c>
       <c r="C367" t="str">
         <v>CAJA PIZZA #24</v>
@@ -11047,7 +11047,7 @@
         <v>581</v>
       </c>
       <c r="B368" t="str">
-        <v>46584 View | Edit | Add opening stock | Delete</v>
+        <v>46584</v>
       </c>
       <c r="C368" t="str">
         <v>CAFE PORCION</v>
@@ -11076,7 +11076,7 @@
         <v>577</v>
       </c>
       <c r="B369" t="str">
-        <v>44192 View | Edit | Add opening stock | Delete</v>
+        <v>44192</v>
       </c>
       <c r="C369" t="str">
         <v>CACAHUATE TRIT</v>
@@ -11105,7 +11105,7 @@
         <v>576</v>
       </c>
       <c r="B370" t="str">
-        <v>87728 View | Edit | Add opening stock | Delete</v>
+        <v>87728</v>
       </c>
       <c r="C370" t="str">
         <v>CACAHUATE TOST</v>
@@ -11134,7 +11134,7 @@
         <v>569</v>
       </c>
       <c r="B371" t="str">
-        <v>37542 View | Edit | Add opening stock | Delete</v>
+        <v>37542</v>
       </c>
       <c r="C371" t="str">
         <v>BOTE DE 1/2Litro</v>
@@ -11163,7 +11163,7 @@
         <v>568</v>
       </c>
       <c r="B372" t="str">
-        <v>66073 View | Edit | Add opening stock | Delete</v>
+        <v>66073</v>
       </c>
       <c r="C372" t="str">
         <v>BOTE 2Litro</v>
@@ -11192,7 +11192,7 @@
         <v>567</v>
       </c>
       <c r="B373" t="str">
-        <v>70108 View | Edit | Add opening stock | Delete</v>
+        <v>70108</v>
       </c>
       <c r="C373" t="str">
         <v>BOLSA ROLLO 15*25</v>
@@ -11221,7 +11221,7 @@
         <v>566</v>
       </c>
       <c r="B374" t="str">
-        <v>54245 View | Edit | Add opening stock | Delete</v>
+        <v>54245</v>
       </c>
       <c r="C374" t="str">
         <v>BOLSA NEGRA</v>
@@ -11250,7 +11250,7 @@
         <v>565</v>
       </c>
       <c r="B375" t="str">
-        <v>18735 View | Edit | Add opening stock | Delete</v>
+        <v>18735</v>
       </c>
       <c r="C375" t="str">
         <v>BOLSA CELOFAN 6*12</v>
@@ -11279,7 +11279,7 @@
         <v>564</v>
       </c>
       <c r="B376" t="str">
-        <v>38342 View | Edit | Add opening stock | Delete</v>
+        <v>38342</v>
       </c>
       <c r="C376" t="str">
         <v>BOLSA CAMISETA MED BIO</v>
@@ -11308,7 +11308,7 @@
         <v>563</v>
       </c>
       <c r="B377" t="str">
-        <v>82213 View | Edit | Add opening stock | Delete</v>
+        <v>82213</v>
       </c>
       <c r="C377" t="str">
         <v>BOLSA CAMISETA BIO GDE</v>
@@ -11337,7 +11337,7 @@
         <v>562</v>
       </c>
       <c r="B378" t="str">
-        <v>40072 View | Edit | Add opening stock | Delete</v>
+        <v>40072</v>
       </c>
       <c r="C378" t="str">
         <v>BOLSA CAM MED</v>
@@ -11366,7 +11366,7 @@
         <v>561</v>
       </c>
       <c r="B379" t="str">
-        <v>42906 View | Edit | Add opening stock | Delete</v>
+        <v>42906</v>
       </c>
       <c r="C379" t="str">
         <v>BOLSA CAM GDE</v>
@@ -11395,7 +11395,7 @@
         <v>560</v>
       </c>
       <c r="B380" t="str">
-        <v>16539 View | Edit | Add opening stock | Delete</v>
+        <v>16539</v>
       </c>
       <c r="C380" t="str">
         <v>BOLSA CAM CH</v>
@@ -11424,7 +11424,7 @@
         <v>559</v>
       </c>
       <c r="B381" t="str">
-        <v>50366 View | Edit | Add opening stock | Delete</v>
+        <v>50366</v>
       </c>
       <c r="C381" t="str">
         <v>BOLSA 60*90 TRANSPARENTE</v>
@@ -11453,7 +11453,7 @@
         <v>558</v>
       </c>
       <c r="B382" t="str">
-        <v>20236 View | Edit | Add opening stock | Delete</v>
+        <v>20236</v>
       </c>
       <c r="C382" t="str">
         <v>BOLSA 40 X 60</v>
@@ -11482,7 +11482,7 @@
         <v>557</v>
       </c>
       <c r="B383" t="str">
-        <v>38354 View | Edit | Add opening stock | Delete</v>
+        <v>38354</v>
       </c>
       <c r="C383" t="str">
         <v>BOLSA 32 X 35 RLLO ALitroA</v>
@@ -11511,7 +11511,7 @@
         <v>556</v>
       </c>
       <c r="B384" t="str">
-        <v>80775 View | Edit | Add opening stock | Delete</v>
+        <v>80775</v>
       </c>
       <c r="C384" t="str">
         <v>BOLSA 25*35</v>
@@ -11540,7 +11540,7 @@
         <v>555</v>
       </c>
       <c r="B385" t="str">
-        <v>20638 View | Edit | Add opening stock | Delete</v>
+        <v>20638</v>
       </c>
       <c r="C385" t="str">
         <v>BOLSA 20*30</v>
@@ -11569,7 +11569,7 @@
         <v>554</v>
       </c>
       <c r="B386" t="str">
-        <v>84311 View | Edit | Add opening stock | Delete</v>
+        <v>84311</v>
       </c>
       <c r="C386" t="str">
         <v>BOLSA 18 X 26</v>
@@ -11598,7 +11598,7 @@
         <v>553</v>
       </c>
       <c r="B387" t="str">
-        <v>64568 View | Edit | Add opening stock | Delete</v>
+        <v>64568</v>
       </c>
       <c r="C387" t="str">
         <v>BOLSA 10X25</v>
@@ -11627,7 +11627,7 @@
         <v>552</v>
       </c>
       <c r="B388" t="str">
-        <v>81784 View | Edit | Add opening stock | Delete</v>
+        <v>81784</v>
       </c>
       <c r="C388" t="str">
         <v>BOLSA 1/2 KG</v>
@@ -11656,7 +11656,7 @@
         <v>539</v>
       </c>
       <c r="B389" t="str">
-        <v>62300 View | Edit | Add opening stock | Delete</v>
+        <v>62300</v>
       </c>
       <c r="C389" t="str">
         <v>AZUCAR KG</v>
@@ -11685,7 +11685,7 @@
         <v>537</v>
       </c>
       <c r="B390" t="str">
-        <v>65494 View | Edit | Add opening stock | Delete</v>
+        <v>65494</v>
       </c>
       <c r="C390" t="str">
         <v>AZUCAR PaqueteTO</v>
@@ -11714,7 +11714,7 @@
         <v>536</v>
       </c>
       <c r="B391" t="str">
-        <v>73555 View | Edit | Add opening stock | Delete</v>
+        <v>73555</v>
       </c>
       <c r="C391" t="str">
         <v>AXION LIQUIDO TRICLORO</v>
@@ -11743,7 +11743,7 @@
         <v>535</v>
       </c>
       <c r="B392" t="str">
-        <v>34229 View | Edit | Add opening stock | Delete</v>
+        <v>34229</v>
       </c>
       <c r="C392" t="str">
         <v>ATUN LATA</v>
@@ -11772,7 +11772,7 @@
         <v>533</v>
       </c>
       <c r="B393" t="str">
-        <v>22635 View | Edit | Add opening stock | Delete</v>
+        <v>22635</v>
       </c>
       <c r="C393" t="str">
         <v>ATUN AGUA LATA CH</v>
@@ -11801,7 +11801,7 @@
         <v>530</v>
       </c>
       <c r="B394" t="str">
-        <v>52643 View | Edit | Add opening stock | Delete</v>
+        <v>52643</v>
       </c>
       <c r="C394" t="str">
         <v>ARROZ QUEBRADO</v>
@@ -11830,7 +11830,7 @@
         <v>523</v>
       </c>
       <c r="B395" t="str">
-        <v>83480 View | Edit | Add opening stock | Delete</v>
+        <v>83480</v>
       </c>
       <c r="C395" t="str">
         <v>ALMENDRA FIL S/C</v>
@@ -11859,7 +11859,7 @@
         <v>518</v>
       </c>
       <c r="B396" t="str">
-        <v>87111 View | Edit | Add opening stock | Delete</v>
+        <v>87111</v>
       </c>
       <c r="C396" t="str">
         <v>AJONJOLI MACARENA</v>
@@ -11888,7 +11888,7 @@
         <v>517</v>
       </c>
       <c r="B397" t="str">
-        <v>20324 View | Edit | Add opening stock | Delete</v>
+        <v>20324</v>
       </c>
       <c r="C397" t="str">
         <v>AJONJOLI C/MIEL</v>
@@ -11917,7 +11917,7 @@
         <v>516</v>
       </c>
       <c r="B398" t="str">
-        <v>51904 View | Edit | Add opening stock | Delete</v>
+        <v>51904</v>
       </c>
       <c r="C398" t="str">
         <v>AJO PZ</v>
@@ -11946,7 +11946,7 @@
         <v>514</v>
       </c>
       <c r="B399" t="str">
-        <v>88979 View | Edit | Add opening stock | Delete</v>
+        <v>88979</v>
       </c>
       <c r="C399" t="str">
         <v>AJO KG</v>
@@ -11975,7 +11975,7 @@
         <v>512</v>
       </c>
       <c r="B400" t="str">
-        <v>83007 View | Edit | Add opening stock | Delete</v>
+        <v>83007</v>
       </c>
       <c r="C400" t="str">
         <v>AJO BOTE GDE</v>
@@ -12004,7 +12004,7 @@
         <v>510</v>
       </c>
       <c r="B401" t="str">
-        <v>59053 View | Edit | Add opening stock | Delete</v>
+        <v>59053</v>
       </c>
       <c r="C401" t="str">
         <v>AGUACATE VDE PZ</v>
@@ -12033,7 +12033,7 @@
         <v>509</v>
       </c>
       <c r="B402" t="str">
-        <v>67965 View | Edit | Add opening stock | Delete</v>
+        <v>67965</v>
       </c>
       <c r="C402" t="str">
         <v>AGUACATE VDE KG</v>
@@ -12062,7 +12062,7 @@
         <v>508</v>
       </c>
       <c r="B403" t="str">
-        <v>21604 View | Edit | Add opening stock | Delete</v>
+        <v>21604</v>
       </c>
       <c r="C403" t="str">
         <v>AGUACATE RAY PZ</v>
@@ -12091,7 +12091,7 @@
         <v>507</v>
       </c>
       <c r="B404" t="str">
-        <v>58487 View | Edit | Add opening stock | Delete</v>
+        <v>58487</v>
       </c>
       <c r="C404" t="str">
         <v>AGUACATE RAY KG</v>
@@ -12120,7 +12120,7 @@
         <v>506</v>
       </c>
       <c r="B405" t="str">
-        <v>39161 View | Edit | Add opening stock | Delete</v>
+        <v>39161</v>
       </c>
       <c r="C405" t="str">
         <v>AGUACATE MAD PZ</v>
@@ -12149,7 +12149,7 @@
         <v>505</v>
       </c>
       <c r="B406" t="str">
-        <v>76265 View | Edit | Add opening stock | Delete</v>
+        <v>76265</v>
       </c>
       <c r="C406" t="str">
         <v>AGUACATE MAD KG</v>
@@ -12178,7 +12178,7 @@
         <v>496</v>
       </c>
       <c r="B407" t="str">
-        <v>15991 View | Edit | Add opening stock | Delete</v>
+        <v>15991</v>
       </c>
       <c r="C407" t="str">
         <v>ACEITE SOYA 20L</v>
@@ -12207,7 +12207,7 @@
         <v>495</v>
       </c>
       <c r="B408" t="str">
-        <v>52108 View | Edit | Add opening stock | Delete</v>
+        <v>52108</v>
       </c>
       <c r="C408" t="str">
         <v>ACEITE PAM CANOLA</v>
@@ -12236,7 +12236,7 @@
         <v>494</v>
       </c>
       <c r="B409" t="str">
-        <v>35096 View | Edit | Add opening stock | Delete</v>
+        <v>35096</v>
       </c>
       <c r="C409" t="str">
         <v>ACEITE OLIVA Galón</v>
@@ -12265,7 +12265,7 @@
         <v>493</v>
       </c>
       <c r="B410" t="str">
-        <v>21015 View | Edit | Add opening stock | Delete</v>
+        <v>21015</v>
       </c>
       <c r="C410" t="str">
         <v>ACEITE OLIVA GALAVIZ</v>
@@ -12294,7 +12294,7 @@
         <v>490</v>
       </c>
       <c r="B411" t="str">
-        <v>53886 View | Edit | Add opening stock | Delete</v>
+        <v>53886</v>
       </c>
       <c r="C411" t="str">
         <v>ACEITE CRISTAL CJ</v>
@@ -12323,7 +12323,7 @@
         <v>489</v>
       </c>
       <c r="B412" t="str">
-        <v>21910 View | Edit | Add opening stock | Delete</v>
+        <v>21910</v>
       </c>
       <c r="C412" t="str">
         <v>ACEITE CRISTAL 5L</v>
@@ -12352,7 +12352,7 @@
         <v>488</v>
       </c>
       <c r="B413" t="str">
-        <v>63585 View | Edit | Add opening stock | Delete</v>
+        <v>63585</v>
       </c>
       <c r="C413" t="str">
         <v>ACEITE CRISTAL 20L</v>
@@ -12381,7 +12381,7 @@
         <v>486</v>
       </c>
       <c r="B414" t="str">
-        <v>17884 View | Edit | Add opening stock | Delete</v>
+        <v>17884</v>
       </c>
       <c r="C414" t="str">
         <v>ACEITE CAPULLO</v>
@@ -12410,7 +12410,7 @@
         <v>485</v>
       </c>
       <c r="B415" t="str">
-        <v>67888 View | Edit | Add opening stock | Delete</v>
+        <v>67888</v>
       </c>
       <c r="C415" t="str">
         <v>ACEITE CACAHUATE TOSTADO INES</v>
@@ -12439,7 +12439,7 @@
         <v>482</v>
       </c>
       <c r="B416" t="str">
-        <v>9999994 View | Edit | Add opening stock | Delete</v>
+        <v>9999994</v>
       </c>
       <c r="C416" t="str">
         <v>ZANAHORIA VINAGRE BOT</v>
@@ -12468,7 +12468,7 @@
         <v>480</v>
       </c>
       <c r="B417" t="str">
-        <v>70141520 View | Edit | Add opening stock | Delete</v>
+        <v>70141520</v>
       </c>
       <c r="C417" t="str">
         <v>ZANAHORIA BABY COLORES</v>
@@ -12497,7 +12497,7 @@
         <v>478</v>
       </c>
       <c r="B418" t="str">
-        <v>999993 View | Edit | Add opening stock | Delete</v>
+        <v>999993</v>
       </c>
       <c r="C418" t="str">
         <v>YUKA KG</v>
@@ -12526,7 +12526,7 @@
         <v>477</v>
       </c>
       <c r="B419" t="str">
-        <v>999992 View | Edit | Add opening stock | Delete</v>
+        <v>999992</v>
       </c>
       <c r="C419" t="str">
         <v>YUKA</v>
@@ -12555,7 +12555,7 @@
         <v>476</v>
       </c>
       <c r="B420" t="str">
-        <v>99999991 View | Edit | Add opening stock | Delete</v>
+        <v>99999991</v>
       </c>
       <c r="C420" t="str">
         <v>YAKULT AZUL</v>
@@ -12584,7 +12584,7 @@
         <v>475</v>
       </c>
       <c r="B421" t="str">
-        <v>48102109 View | Edit | Add opening stock | Delete</v>
+        <v>48102109</v>
       </c>
       <c r="C421" t="str">
         <v>VITAFIL BOBINA</v>
@@ -12613,7 +12613,7 @@
         <v>469</v>
       </c>
       <c r="B422" t="str">
-        <v>52141524 View | Edit | Add opening stock | Delete</v>
+        <v>52141524</v>
       </c>
       <c r="C422" t="str">
         <v>VASO D LICUADORA</v>
@@ -12642,7 +12642,7 @@
         <v>463</v>
       </c>
       <c r="B423" t="str">
-        <v>50192600 View | Edit | Add opening stock | Delete</v>
+        <v>50192600</v>
       </c>
       <c r="C423" t="str">
         <v>TORTA D PAPA</v>
@@ -12671,7 +12671,7 @@
         <v>459</v>
       </c>
       <c r="B424" t="str">
-        <v>50406506 View | Edit | Add opening stock | Delete</v>
+        <v>50406506</v>
       </c>
       <c r="C424" t="str">
         <v>TOMATE CHERRY BUR</v>
@@ -12700,7 +12700,7 @@
         <v>458</v>
       </c>
       <c r="B425" t="str">
-        <v>52121703 View | Edit | Add opening stock | Delete</v>
+        <v>52121703</v>
       </c>
       <c r="C425" t="str">
         <v>TOLLA MICROFIBRA</v>
@@ -12729,7 +12729,7 @@
         <v>457</v>
       </c>
       <c r="B426" t="str">
-        <v>47121804 View | Edit | Add opening stock | Delete</v>
+        <v>47121804</v>
       </c>
       <c r="C426" t="str">
         <v>TINA</v>
@@ -12758,7 +12758,7 @@
         <v>453</v>
       </c>
       <c r="B427" t="str">
-        <v>52101500 View | Edit | Add opening stock | Delete</v>
+        <v>52101500</v>
       </c>
       <c r="C427" t="str">
         <v>TAPETE</v>
@@ -12787,7 +12787,7 @@
         <v>450</v>
       </c>
       <c r="B428" t="str">
-        <v>50347037 View | Edit | Add opening stock | Delete</v>
+        <v>50347037</v>
       </c>
       <c r="C428" t="str">
         <v>TAMARINDO CONCENTRADO</v>
@@ -12816,7 +12816,7 @@
         <v>448</v>
       </c>
       <c r="B429" t="str">
-        <v>50201714 View | Edit | Add opening stock | Delete</v>
+        <v>50201714</v>
       </c>
       <c r="C429" t="str">
         <v>SUSTITUTO CREMA P/CAFE CORINA 1K</v>
@@ -12845,7 +12845,7 @@
         <v>443</v>
       </c>
       <c r="B430" t="str">
-        <v>31133710 View | Edit | Add opening stock | Delete</v>
+        <v>31133710</v>
       </c>
       <c r="C430" t="str">
         <v>SILICON TRANSPARENTE</v>
@@ -12874,7 +12874,7 @@
         <v>442</v>
       </c>
       <c r="B431" t="str">
-        <v>50404822 View | Edit | Add opening stock | Delete</v>
+        <v>50404822</v>
       </c>
       <c r="C431" t="str">
         <v>SETAS</v>
@@ -12903,7 +12903,7 @@
         <v>441</v>
       </c>
       <c r="B432" t="str">
-        <v>52121602 View | Edit | Add opening stock | Delete</v>
+        <v>52121602</v>
       </c>
       <c r="C432" t="str">
         <v>SERVILLETA TELA</v>
@@ -12932,7 +12932,7 @@
         <v>440</v>
       </c>
       <c r="B433" t="str">
-        <v>14111705 View | Edit | Add opening stock | Delete</v>
+        <v>14111705</v>
       </c>
       <c r="C433" t="str">
         <v>SERVILLETA CAJA</v>
@@ -12961,7 +12961,7 @@
         <v>439</v>
       </c>
       <c r="B434" t="str">
-        <v>10151810 View | Edit | Add opening stock | Delete</v>
+        <v>10151810</v>
       </c>
       <c r="C434" t="str">
         <v>SEMILLA MOSTAZA</v>
@@ -12990,7 +12990,7 @@
         <v>438</v>
       </c>
       <c r="B435" t="str">
-        <v>10151904 View | Edit | Add opening stock | Delete</v>
+        <v>10151904</v>
       </c>
       <c r="C435" t="str">
         <v>SEMILLA DE GIRASOL</v>
@@ -13019,7 +13019,7 @@
         <v>436</v>
       </c>
       <c r="B436" t="str">
-        <v>50304657 View | Edit | Add opening stock | Delete</v>
+        <v>50304657</v>
       </c>
       <c r="C436" t="str">
         <v>SANDIA SIN SEMILLA KG</v>
@@ -13048,7 +13048,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="str">
-        <v>50404121 View | Edit | Add opening stock | Delete</v>
+        <v>50404121</v>
       </c>
       <c r="C437" t="str">
         <v>SALVIA Manojo</v>
@@ -13077,7 +13077,7 @@
         <v>434</v>
       </c>
       <c r="B438" t="str">
-        <v>10121501 View | Edit | Add opening stock | Delete</v>
+        <v>10121501</v>
       </c>
       <c r="C438" t="str">
         <v>SALVADO</v>
@@ -13106,7 +13106,7 @@
         <v>433</v>
       </c>
       <c r="B439" t="str">
-        <v>50172001 View | Edit | Add opening stock | Delete</v>
+        <v>50172001</v>
       </c>
       <c r="C439" t="str">
         <v>SALSA SOYA</v>
@@ -13135,7 +13135,7 @@
         <v>422</v>
       </c>
       <c r="B440" t="str">
-        <v>50131803 View | Edit | Add opening stock | Delete</v>
+        <v>50131803</v>
       </c>
       <c r="C440" t="str">
         <v>QUESO AMARILLO</v>
@@ -13164,7 +13164,7 @@
         <v>418</v>
       </c>
       <c r="B441" t="str">
-        <v>52151507 View | Edit | Add opening stock | Delete</v>
+        <v>52151507</v>
       </c>
       <c r="C441" t="str">
         <v>POPOTES EXTRA GDE</v>
@@ -13193,7 +13193,7 @@
         <v>417</v>
       </c>
       <c r="B442" t="str">
-        <v>50111520 View | Edit | Add opening stock | Delete</v>
+        <v>50111520</v>
       </c>
       <c r="C442" t="str">
         <v>POLLO/KG</v>
@@ -13222,7 +13222,7 @@
         <v>415</v>
       </c>
       <c r="B443" t="str">
-        <v>50405632 View | Edit | Add opening stock | Delete</v>
+        <v>50405632</v>
       </c>
       <c r="C443" t="str">
         <v>POBLANO KG</v>
@@ -13251,7 +13251,7 @@
         <v>414</v>
       </c>
       <c r="B444" t="str">
-        <v>52151502 View | Edit | Add opening stock | Delete</v>
+        <v>52151502</v>
       </c>
       <c r="C444" t="str">
         <v>PLATO DE CarteraON</v>
@@ -13280,7 +13280,7 @@
         <v>412</v>
       </c>
       <c r="B445" t="str">
-        <v>50301700 View | Edit | Add opening stock | Delete</v>
+        <v>50301700</v>
       </c>
       <c r="C445" t="str">
         <v>PLATANO TABASCO ALIMONADO CJ</v>
@@ -13309,7 +13309,7 @@
         <v>410</v>
       </c>
       <c r="B446" t="str">
-        <v>50307025 View | Edit | Add opening stock | Delete</v>
+        <v>50307025</v>
       </c>
       <c r="C446" t="str">
         <v>PLATANO MACHO MADURO KG</v>
@@ -13338,7 +13338,7 @@
         <v>406</v>
       </c>
       <c r="B447" t="str">
-        <v>50365600 View | Edit | Add opening stock | Delete</v>
+        <v>50365600</v>
       </c>
       <c r="C447" t="str">
         <v>PIÑA EN ALMIBAR</v>
@@ -13367,7 +13367,7 @@
         <v>405</v>
       </c>
       <c r="B448" t="str">
-        <v>50305600 View | Edit | Add opening stock | Delete</v>
+        <v>50305600</v>
       </c>
       <c r="C448" t="str">
         <v>PIÑA CAYENA MADURA</v>
@@ -13396,7 +13396,7 @@
         <v>404</v>
       </c>
       <c r="B449" t="str">
-        <v>50161509 View | Edit | Add opening stock | Delete</v>
+        <v>50161509</v>
       </c>
       <c r="C449" t="str">
         <v>PILONCILLO CLARO</v>
@@ -13425,7 +13425,7 @@
         <v>403</v>
       </c>
       <c r="B450" t="str">
-        <v>27111908 View | Edit | Add opening stock | Delete</v>
+        <v>27111908</v>
       </c>
       <c r="C450" t="str">
         <v>PIEDRA P/ALIFAR</v>
@@ -13454,7 +13454,7 @@
         <v>402</v>
       </c>
       <c r="B451" t="str">
-        <v>11111610 View | Edit | Add opening stock | Delete</v>
+        <v>11111610</v>
       </c>
       <c r="C451" t="str">
         <v>PIEDRA</v>
@@ -13483,7 +13483,7 @@
         <v>398</v>
       </c>
       <c r="B452" t="str">
-        <v>50307024 View | Edit | Add opening stock | Delete</v>
+        <v>50307024</v>
       </c>
       <c r="C452" t="str">
         <v>PEPINO AME KG</v>
@@ -13512,7 +13512,7 @@
         <v>397</v>
       </c>
       <c r="B453" t="str">
-        <v>50367024 View | Edit | Add opening stock | Delete</v>
+        <v>50367024</v>
       </c>
       <c r="C453" t="str">
         <v>PEPINILLO SAN MIGUEL</v>
@@ -13541,7 +13541,7 @@
         <v>396</v>
       </c>
       <c r="B454" t="str">
-        <v>1111132 View | Edit | Add opening stock | Delete</v>
+        <v>1111132</v>
       </c>
       <c r="C454" t="str">
         <v>PELOTAS</v>
@@ -13570,7 +13570,7 @@
         <v>391</v>
       </c>
       <c r="B455" t="str">
-        <v>50192902 View | Edit | Add opening stock | Delete</v>
+        <v>50192902</v>
       </c>
       <c r="C455" t="str">
         <v>PASTA FILO</v>
@@ -13599,7 +13599,7 @@
         <v>390</v>
       </c>
       <c r="B456" t="str">
-        <v>31201602 View | Edit | Add opening stock | Delete</v>
+        <v>31201602</v>
       </c>
       <c r="C456" t="str">
         <v>PASTA</v>
@@ -13628,7 +13628,7 @@
         <v>387</v>
       </c>
       <c r="B457" t="str">
-        <v>50407049 View | Edit | Add opening stock | Delete</v>
+        <v>50407049</v>
       </c>
       <c r="C457" t="str">
         <v>PAPRICA</v>
@@ -13657,7 +13657,7 @@
         <v>383</v>
       </c>
       <c r="B458" t="str">
-        <v>24141506 View | Edit | Add opening stock | Delete</v>
+        <v>24141506</v>
       </c>
       <c r="C458" t="str">
         <v>PAPEL ESTRELLA</v>
@@ -13686,7 +13686,7 @@
         <v>382</v>
       </c>
       <c r="B459" t="str">
-        <v>14111500 View | Edit | Add opening stock | Delete</v>
+        <v>14111500</v>
       </c>
       <c r="C459" t="str">
         <v>PAPEL ENCERADO</v>
@@ -13715,7 +13715,7 @@
         <v>379</v>
       </c>
       <c r="B460" t="str">
-        <v>50305102 View | Edit | Add opening stock | Delete</v>
+        <v>50305102</v>
       </c>
       <c r="C460" t="str">
         <v>PAPAYA MAD CJ</v>
@@ -13744,7 +13744,7 @@
         <v>378</v>
       </c>
       <c r="B461" t="str">
-        <v>50405700 View | Edit | Add opening stock | Delete</v>
+        <v>50405700</v>
       </c>
       <c r="C461" t="str">
         <v>PAPA 1A AMARILLA PZ</v>
@@ -13773,7 +13773,7 @@
         <v>377</v>
       </c>
       <c r="B462" t="str">
-        <v>50131800 View | Edit | Add opening stock | Delete</v>
+        <v>50131800</v>
       </c>
       <c r="C462" t="str">
         <v>PANELA LALA 200GR</v>
@@ -13802,7 +13802,7 @@
         <v>373</v>
       </c>
       <c r="B463" t="str">
-        <v>53131507 View | Edit | Add opening stock | Delete</v>
+        <v>53131507</v>
       </c>
       <c r="C463" t="str">
         <v>PALILLO ESTUCHADO</v>
@@ -13831,7 +13831,7 @@
         <v>364</v>
       </c>
       <c r="B464" t="str">
-        <v>50305000 View | Edit | Add opening stock | Delete</v>
+        <v>50305000</v>
       </c>
       <c r="C464" t="str">
         <v>NARANJA KG</v>
@@ -13860,7 +13860,7 @@
         <v>361</v>
       </c>
       <c r="B465" t="str">
-        <v>1111131 View | Edit | Add opening stock | Delete</v>
+        <v>1111131</v>
       </c>
       <c r="C465" t="str">
         <v>MOSTAZA DIJON 865GR</v>
@@ -13889,7 +13889,7 @@
         <v>357</v>
       </c>
       <c r="B466" t="str">
-        <v>50405631 View | Edit | Add opening stock | Delete</v>
+        <v>50405631</v>
       </c>
       <c r="C466" t="str">
         <v>MORRON AMARILLO CJ</v>
@@ -13918,7 +13918,7 @@
         <v>355</v>
       </c>
       <c r="B467" t="str">
-        <v>MLitro View | Edit | Add opening stock | Delete</v>
+        <v>MLitro</v>
       </c>
       <c r="C467" t="str">
         <v>MODELO ESP</v>
@@ -13947,7 +13947,7 @@
         <v>354</v>
       </c>
       <c r="B468" t="str">
-        <v>50111515 View | Edit | Add opening stock | Delete</v>
+        <v>50111515</v>
       </c>
       <c r="C468" t="str">
         <v>MILANESA DE POLLO</v>
@@ -13976,7 +13976,7 @@
         <v>351</v>
       </c>
       <c r="B469" t="str">
-        <v>47131803 View | Edit | Add opening stock | Delete</v>
+        <v>47131803</v>
       </c>
       <c r="C469" t="str">
         <v>MICRODIN</v>
@@ -14005,7 +14005,7 @@
         <v>339</v>
       </c>
       <c r="B470" t="str">
-        <v>50301500 View | Edit | Add opening stock | Delete</v>
+        <v>50301500</v>
       </c>
       <c r="C470" t="str">
         <v>MANZANA ESCOLAR</v>
@@ -14034,7 +14034,7 @@
         <v>337</v>
       </c>
       <c r="B471" t="str">
-        <v>50151600 View | Edit | Add opening stock | Delete</v>
+        <v>50151600</v>
       </c>
       <c r="C471" t="str">
         <v>MANTECA CUBETA TEPA 3.8</v>
@@ -14063,7 +14063,7 @@
         <v>334</v>
       </c>
       <c r="B472" t="str">
-        <v>50364500 View | Edit | Add opening stock | Delete</v>
+        <v>50364500</v>
       </c>
       <c r="C472" t="str">
         <v>MANGO LATA</v>
@@ -14092,7 +14092,7 @@
         <v>333</v>
       </c>
       <c r="B473" t="str">
-        <v>50344500 View | Edit | Add opening stock | Delete</v>
+        <v>50344500</v>
       </c>
       <c r="C473" t="str">
         <v>MANGO CONGELADO BOLSA</v>
@@ -14121,7 +14121,7 @@
         <v>332</v>
       </c>
       <c r="B474" t="str">
-        <v>50304500 View | Edit | Add opening stock | Delete</v>
+        <v>50304500</v>
       </c>
       <c r="C474" t="str">
         <v>MANGO BARRANQUEÑO</v>
@@ -14150,7 +14150,7 @@
         <v>326</v>
       </c>
       <c r="B475" t="str">
-        <v>50403200 View | Edit | Add opening stock | Delete</v>
+        <v>50403200</v>
       </c>
       <c r="C475" t="str">
         <v>MAIZ POZOLERO BCO</v>
@@ -14179,7 +14179,7 @@
         <v>307</v>
       </c>
       <c r="B476" t="str">
-        <v>1111127 View | Edit | Add opening stock | Delete</v>
+        <v>1111127</v>
       </c>
       <c r="C476" t="str">
         <v>JUGO NARANJA SELLO ROJO</v>
@@ -14208,7 +14208,7 @@
         <v>301</v>
       </c>
       <c r="B477" t="str">
-        <v>50406502 View | Edit | Add opening stock | Delete</v>
+        <v>50406502</v>
       </c>
       <c r="C477" t="str">
         <v>JITOMATE BOLA RAY CJ</v>
@@ -14237,7 +14237,7 @@
         <v>300</v>
       </c>
       <c r="B478" t="str">
-        <v>50406500 View | Edit | Add opening stock | Delete</v>
+        <v>50406500</v>
       </c>
       <c r="C478" t="str">
         <v>JITIOMATE SALADET 2A RAY CJ</v>
@@ -14266,7 +14266,7 @@
         <v>296</v>
       </c>
       <c r="B479" t="str">
-        <v>10314000 View | Edit | Add opening stock | Delete</v>
+        <v>10314000</v>
       </c>
       <c r="C479" t="str">
         <v>JENGIBRE KG</v>
@@ -14295,7 +14295,7 @@
         <v>295</v>
       </c>
       <c r="B480" t="str">
-        <v>50161512 View | Edit | Add opening stock | Delete</v>
+        <v>50161512</v>
       </c>
       <c r="C480" t="str">
         <v>JARABE NATURAL</v>
@@ -14324,7 +14324,7 @@
         <v>294</v>
       </c>
       <c r="B481" t="str">
-        <v>50112000 View | Edit | Add opening stock | Delete</v>
+        <v>50112000</v>
       </c>
       <c r="C481" t="str">
         <v>JAMON ROSS PIERNA</v>
@@ -14353,7 +14353,7 @@
         <v>288</v>
       </c>
       <c r="B482" t="str">
-        <v>47121611 View | Edit | Add opening stock | Delete</v>
+        <v>47121611</v>
       </c>
       <c r="C482" t="str">
         <v>JALADOR DE PISOS</v>
@@ -14382,7 +14382,7 @@
         <v>287</v>
       </c>
       <c r="B483" t="str">
-        <v>1111124 View | Edit | Add opening stock | Delete</v>
+        <v>1111124</v>
       </c>
       <c r="C483" t="str">
         <v>JABON LIRIO NEUTRO</v>
@@ -14411,7 +14411,7 @@
         <v>283</v>
       </c>
       <c r="B484" t="str">
-        <v>1111123 View | Edit | Add opening stock | Delete</v>
+        <v>1111123</v>
       </c>
       <c r="C484" t="str">
         <v>HORNO TOSTADOR VIOS</v>
@@ -14440,7 +14440,7 @@
         <v>282</v>
       </c>
       <c r="B485" t="str">
-        <v>1111122 View | Edit | Add opening stock | Delete</v>
+        <v>1111122</v>
       </c>
       <c r="C485" t="str">
         <v>HORNO TOSTADOR OSTER</v>
@@ -14469,7 +14469,7 @@
         <v>281</v>
       </c>
       <c r="B486" t="str">
-        <v>1111121 View | Edit | Add opening stock | Delete</v>
+        <v>1111121</v>
       </c>
       <c r="C486" t="str">
         <v>HORNO ELECTRICO TAURUS</v>
@@ -14498,7 +14498,7 @@
         <v>280</v>
       </c>
       <c r="B487" t="str">
-        <v>1111120 View | Edit | Add opening stock | Delete</v>
+        <v>1111120</v>
       </c>
       <c r="C487" t="str">
         <v>HORNO DE MICROONDAS OSTER</v>
@@ -14527,7 +14527,7 @@
         <v>267</v>
       </c>
       <c r="B488" t="str">
-        <v>50221301 View | Edit | Add opening stock | Delete</v>
+        <v>50221301</v>
       </c>
       <c r="C488" t="str">
         <v>HARINA PaqueteTO</v>
@@ -14556,7 +14556,7 @@
         <v>250</v>
       </c>
       <c r="B489" t="str">
-        <v>50407018 View | Edit | Add opening stock | Delete</v>
+        <v>50407018</v>
       </c>
       <c r="C489" t="str">
         <v>GARBANZA</v>
@@ -14585,7 +14585,7 @@
         <v>246</v>
       </c>
       <c r="B490" t="str">
-        <v>50171901 View | Edit | Add opening stock | Delete</v>
+        <v>50171901</v>
       </c>
       <c r="C490" t="str">
         <v>FRUTA EN VINAGRE</v>
@@ -14614,7 +14614,7 @@
         <v>242</v>
       </c>
       <c r="B491" t="str">
-        <v>50306700 View | Edit | Add opening stock | Delete</v>
+        <v>50306700</v>
       </c>
       <c r="C491" t="str">
         <v>FRESA BUR</v>
@@ -14643,7 +14643,7 @@
         <v>237</v>
       </c>
       <c r="B492" t="str">
-        <v>50192901 View | Edit | Add opening stock | Delete</v>
+        <v>50192901</v>
       </c>
       <c r="C492" t="str">
         <v>FETUCCINI PQTE</v>
@@ -14672,7 +14672,7 @@
         <v>236</v>
       </c>
       <c r="B493" t="str">
-        <v>47131801 View | Edit | Add opening stock | Delete</v>
+        <v>47131801</v>
       </c>
       <c r="C493" t="str">
         <v>FAPaqueteOSO</v>
@@ -14701,7 +14701,7 @@
         <v>229</v>
       </c>
       <c r="B494" t="str">
-        <v>50401600 View | Edit | Add opening stock | Delete</v>
+        <v>50401600</v>
       </c>
       <c r="C494" t="str">
         <v>ESPARRAGO DELGADO</v>
@@ -14730,7 +14730,7 @@
         <v>228</v>
       </c>
       <c r="B495" t="str">
-        <v>50192900 View | Edit | Add opening stock | Delete</v>
+        <v>50192900</v>
       </c>
       <c r="C495" t="str">
         <v>ESPAGUETTI BARILLA</v>
@@ -14759,7 +14759,7 @@
         <v>227</v>
       </c>
       <c r="B496" t="str">
-        <v>51212001 View | Edit | Add opening stock | Delete</v>
+        <v>51212001</v>
       </c>
       <c r="C496" t="str">
         <v>ESENCIA</v>
@@ -14788,7 +14788,7 @@
         <v>223</v>
       </c>
       <c r="B497" t="str">
-        <v>13111215 View | Edit | Add opening stock | Delete</v>
+        <v>13111215</v>
       </c>
       <c r="C497" t="str">
         <v>ENVOLitroURA DE PLASTICO</v>
@@ -14817,7 +14817,7 @@
         <v>220</v>
       </c>
       <c r="B498" t="str">
-        <v>50193201 View | Edit | Add opening stock | Delete</v>
+        <v>50193201</v>
       </c>
       <c r="C498" t="str">
         <v>ENSALADA ITALIANA</v>
@@ -14846,7 +14846,7 @@
         <v>217</v>
       </c>
       <c r="B499" t="str">
-        <v>50403600 View | Edit | Add opening stock | Delete</v>
+        <v>50403600</v>
       </c>
       <c r="C499" t="str">
         <v>ENDIVIAS</v>
@@ -14875,7 +14875,7 @@
         <v>216</v>
       </c>
       <c r="B500" t="str">
-        <v>50211608 View | Edit | Add opening stock | Delete</v>
+        <v>50211608</v>
       </c>
       <c r="C500" t="str">
         <v>ENCENDEDOR TOKAI</v>
@@ -14904,7 +14904,7 @@
         <v>203</v>
       </c>
       <c r="B501" t="str">
-        <v>47131821 View | Edit | Add opening stock | Delete</v>
+        <v>47131821</v>
       </c>
       <c r="C501" t="str">
         <v>DESENGRASANTE</v>
@@ -14933,7 +14933,7 @@
         <v>202</v>
       </c>
       <c r="B502" t="str">
-        <v>50112021 View | Edit | Add opening stock | Delete</v>
+        <v>50112021</v>
       </c>
       <c r="C502" t="str">
         <v>DEMIGLASE KNORR 4K</v>
@@ -14962,7 +14962,7 @@
         <v>201</v>
       </c>
       <c r="B503" t="str">
-        <v>50131802 View | Edit | Add opening stock | Delete</v>
+        <v>50131802</v>
       </c>
       <c r="C503" t="str">
         <v>DEDOS DE QUESO</v>
@@ -14991,7 +14991,7 @@
         <v>182</v>
       </c>
       <c r="B504" t="str">
-        <v>50193104 View | Edit | Add opening stock | Delete</v>
+        <v>50193104</v>
       </c>
       <c r="C504" t="str">
         <v>CONSOME BOTE</v>
@@ -15020,7 +15020,7 @@
         <v>180</v>
       </c>
       <c r="B505" t="str">
-        <v>50202423 View | Edit | Add opening stock | Delete</v>
+        <v>50202423</v>
       </c>
       <c r="C505" t="str">
         <v>CONCENTRADO ZELitroIK</v>
@@ -15049,7 +15049,7 @@
         <v>178</v>
       </c>
       <c r="B506" t="str">
-        <v>50202800 View | Edit | Add opening stock | Delete</v>
+        <v>50202800</v>
       </c>
       <c r="C506" t="str">
         <v>CONCENTRADO TAMARINDO PRINCESA</v>
@@ -15078,7 +15078,7 @@
         <v>177</v>
       </c>
       <c r="B507" t="str">
-        <v>50307503 View | Edit | Add opening stock | Delete</v>
+        <v>50307503</v>
       </c>
       <c r="C507" t="str">
         <v>CONCENTRADO FRUTOS ROJOS</v>
@@ -15107,7 +15107,7 @@
         <v>176</v>
       </c>
       <c r="B508" t="str">
-        <v>50202600 View | Edit | Add opening stock | Delete</v>
+        <v>50202600</v>
       </c>
       <c r="C508" t="str">
         <v>CONCENTRADO F-DIAZ FRESA</v>
@@ -15136,7 +15136,7 @@
         <v>175</v>
       </c>
       <c r="B509" t="str">
-        <v>50202311 View | Edit | Add opening stock | Delete</v>
+        <v>50202311</v>
       </c>
       <c r="C509" t="str">
         <v>CONCENTRADO F DIAZ</v>
@@ -15165,7 +15165,7 @@
         <v>159</v>
       </c>
       <c r="B510" t="str">
-        <v>50345800 View | Edit | Add opening stock | Delete</v>
+        <v>50345800</v>
       </c>
       <c r="C510" t="str">
         <v>CIRUELA CONGELADA</v>
@@ -15194,7 +15194,7 @@
         <v>157</v>
       </c>
       <c r="B511" t="str">
-        <v>31201513 View | Edit | Add opening stock | Delete</v>
+        <v>31201513</v>
       </c>
       <c r="C511" t="str">
         <v>CINTA ANTIDERRAPANT</v>
@@ -15223,7 +15223,7 @@
         <v>151</v>
       </c>
       <c r="B512" t="str">
-        <v>10226020 View | Edit | Add opening stock | Delete</v>
+        <v>10226020</v>
       </c>
       <c r="C512" t="str">
         <v>CHOCOMILK MORELIA</v>
@@ -15252,7 +15252,7 @@
         <v>150</v>
       </c>
       <c r="B513" t="str">
-        <v>1111113 View | Edit | Add opening stock | Delete</v>
+        <v>1111113</v>
       </c>
       <c r="C513" t="str">
         <v>CHOCOLATE CJ</v>
@@ -15281,7 +15281,7 @@
         <v>148</v>
       </c>
       <c r="B514" t="str">
-        <v>50465500 View | Edit | Add opening stock | Delete</v>
+        <v>50465500</v>
       </c>
       <c r="C514" t="str">
         <v>CHIPOTLE LA MORENA</v>
@@ -15310,7 +15310,7 @@
         <v>146</v>
       </c>
       <c r="B515" t="str">
-        <v>50405634 View | Edit | Add opening stock | Delete</v>
+        <v>50405634</v>
       </c>
       <c r="C515" t="str">
         <v>CHILE SERRANO CH KG</v>
@@ -15339,7 +15339,7 @@
         <v>142</v>
       </c>
       <c r="B516" t="str">
-        <v>50405621 View | Edit | Add opening stock | Delete</v>
+        <v>50405621</v>
       </c>
       <c r="C516" t="str">
         <v>CHILE GUAJILLO</v>
@@ -15368,7 +15368,7 @@
         <v>138</v>
       </c>
       <c r="B517" t="str">
-        <v>50466800 View | Edit | Add opening stock | Delete</v>
+        <v>50466800</v>
       </c>
       <c r="C517" t="str">
         <v>CHICHARO /LATA</v>
@@ -15397,7 +15397,7 @@
         <v>133</v>
       </c>
       <c r="B518" t="str">
-        <v>50464800 View | Edit | Add opening stock | Delete</v>
+        <v>50464800</v>
       </c>
       <c r="C518" t="str">
         <v>CHAMPIÑON LAT</v>
@@ -15426,7 +15426,7 @@
         <v>132</v>
       </c>
       <c r="B519" t="str">
-        <v>50404800 View | Edit | Add opening stock | Delete</v>
+        <v>50404800</v>
       </c>
       <c r="C519" t="str">
         <v>CHAMPIÑON BLANCO Cartera</v>
@@ -15455,7 +15455,7 @@
         <v>131</v>
       </c>
       <c r="B520" t="str">
-        <v>50327000 View | Edit | Add opening stock | Delete</v>
+        <v>50327000</v>
       </c>
       <c r="C520" t="str">
         <v>CHABACANO DESHIDRATADDO</v>
@@ -15484,7 +15484,7 @@
         <v>130</v>
       </c>
       <c r="B521" t="str">
-        <v>50405630 View | Edit | Add opening stock | Delete</v>
+        <v>50405630</v>
       </c>
       <c r="C521" t="str">
         <v>CH PIQUIN</v>
@@ -15513,7 +15513,7 @@
         <v>129</v>
       </c>
       <c r="B522" t="str">
-        <v>50405602 View | Edit | Add opening stock | Delete</v>
+        <v>50405602</v>
       </c>
       <c r="C522" t="str">
         <v>CH ARBOL TOST</v>
@@ -15542,7 +15542,7 @@
         <v>125</v>
       </c>
       <c r="B523" t="str">
-        <v>50221100 View | Edit | Add opening stock | Delete</v>
+        <v>50221100</v>
       </c>
       <c r="C523" t="str">
         <v>CEREAL KG</v>
@@ -15571,7 +15571,7 @@
         <v>123</v>
       </c>
       <c r="B524" t="str">
-        <v>1111111 View | Edit | Add opening stock | Delete</v>
+        <v>1111111</v>
       </c>
       <c r="C524" t="str">
         <v>CELULAR MOTOROLA E 14</v>
@@ -15600,7 +15600,7 @@
         <v>118</v>
       </c>
       <c r="B525" t="str">
-        <v>50202201 View | Edit | Add opening stock | Delete</v>
+        <v>50202201</v>
       </c>
       <c r="C525" t="str">
         <v>CarteraA BCA CAGUAMITA</v>
@@ -15629,7 +15629,7 @@
         <v>116</v>
       </c>
       <c r="B526" t="str">
-        <v>10101511 View | Edit | Add opening stock | Delete</v>
+        <v>10101511</v>
       </c>
       <c r="C526" t="str">
         <v>CARNE DE CERDO</v>
@@ -15658,7 +15658,7 @@
         <v>115</v>
       </c>
       <c r="B527" t="str">
-        <v>10502900 View | Edit | Add opening stock | Delete</v>
+        <v>10502900</v>
       </c>
       <c r="C527" t="str">
         <v>CARDONOMO</v>
@@ -15687,7 +15687,7 @@
         <v>110</v>
       </c>
       <c r="B528" t="str">
-        <v>60122506 View | Edit | Add opening stock | Delete</v>
+        <v>60122506</v>
       </c>
       <c r="C528" t="str">
         <v>CAPACILLOS</v>
@@ -15716,7 +15716,7 @@
         <v>104</v>
       </c>
       <c r="B529" t="str">
-        <v>50425500 View | Edit | Add opening stock | Delete</v>
+        <v>50425500</v>
       </c>
       <c r="C529" t="str">
         <v>CALIFORNIA KG</v>
@@ -15745,7 +15745,7 @@
         <v>102</v>
       </c>
       <c r="B530" t="str">
-        <v>73131501 View | Edit | Add opening stock | Delete</v>
+        <v>73131501</v>
       </c>
       <c r="C530" t="str">
         <v>CALAHUA</v>
@@ -15774,7 +15774,7 @@
         <v>99</v>
       </c>
       <c r="B531" t="str">
-        <v>XPK View | Edit | Add opening stock | Delete</v>
+        <v>XPK</v>
       </c>
       <c r="C531" t="str">
         <v>CAJA PIZZA 32*32</v>
@@ -15803,7 +15803,7 @@
         <v>97</v>
       </c>
       <c r="B532" t="str">
-        <v>50201700 View | Edit | Add opening stock | Delete</v>
+        <v>50201700</v>
       </c>
       <c r="C532" t="str">
         <v>CAFE SOBRE</v>
@@ -15832,7 +15832,7 @@
         <v>91</v>
       </c>
       <c r="B533" t="str">
-        <v>50172005 View | Edit | Add opening stock | Delete</v>
+        <v>50172005</v>
       </c>
       <c r="C533" t="str">
         <v>BROTES</v>
@@ -15861,7 +15861,7 @@
         <v>86</v>
       </c>
       <c r="B534" t="str">
-        <v>52151602 View | Edit | Add opening stock | Delete</v>
+        <v>52151602</v>
       </c>
       <c r="C534" t="str">
         <v>BOWLES</v>
@@ -15890,7 +15890,7 @@
         <v>84</v>
       </c>
       <c r="B535" t="str">
-        <v>24122000 View | Edit | Add opening stock | Delete</v>
+        <v>24122000</v>
       </c>
       <c r="C535" t="str">
         <v>BOTE 4LitroO</v>
@@ -15919,7 +15919,7 @@
         <v>83</v>
       </c>
       <c r="B536" t="str">
-        <v>24122002 View | Edit | Add opening stock | Delete</v>
+        <v>24122002</v>
       </c>
       <c r="C536" t="str">
         <v>BOTE 1Litro</v>
@@ -15948,7 +15948,7 @@
         <v>81</v>
       </c>
       <c r="B537" t="str">
-        <v>53111500 View | Edit | Add opening stock | Delete</v>
+        <v>53111500</v>
       </c>
       <c r="C537" t="str">
         <v>BOTAS</v>
@@ -15977,7 +15977,7 @@
         <v>80</v>
       </c>
       <c r="B538" t="str">
-        <v>50192100 View | Edit | Add opening stock | Delete</v>
+        <v>50192100</v>
       </c>
       <c r="C538" t="str">
         <v>BOTANA</v>
@@ -16006,7 +16006,7 @@
         <v>79</v>
       </c>
       <c r="B539" t="str">
-        <v>24111502 View | Edit | Add opening stock | Delete</v>
+        <v>24111502</v>
       </c>
       <c r="C539" t="str">
         <v>BOLSA PAPEL KRAFT CHICA</v>
@@ -16035,7 +16035,7 @@
         <v>78</v>
       </c>
       <c r="B540" t="str">
-        <v>111111 View | Edit | Add opening stock | Delete</v>
+        <v>111111</v>
       </c>
       <c r="C540" t="str">
         <v>BOLSA PAPEL KARFT GRANDE</v>
@@ -16064,7 +16064,7 @@
         <v>77</v>
       </c>
       <c r="B541" t="str">
-        <v>24111503 View | Edit | Add opening stock | Delete</v>
+        <v>24111503</v>
       </c>
       <c r="C541" t="str">
         <v>BOLSA</v>
@@ -16093,7 +16093,7 @@
         <v>75</v>
       </c>
       <c r="B542" t="str">
-        <v>11111138 View | Edit | Add opening stock | Delete</v>
+        <v>11111138</v>
       </c>
       <c r="C542" t="str">
         <v>BOCINA BLUETOOTH VIOS</v>
@@ -16122,7 +16122,7 @@
         <v>74</v>
       </c>
       <c r="B543" t="str">
-        <v>50302000 View | Edit | Add opening stock | Delete</v>
+        <v>50302000</v>
       </c>
       <c r="C543" t="str">
         <v>BLUEBERRY BUR</v>
@@ -16151,7 +16151,7 @@
         <v>73</v>
       </c>
       <c r="B544" t="str">
-        <v>50302003 View | Edit | Add opening stock | Delete</v>
+        <v>50302003</v>
       </c>
       <c r="C544" t="str">
         <v>BLUEBERRY BOTE</v>
@@ -16180,7 +16180,7 @@
         <v>68</v>
       </c>
       <c r="B545" t="str">
-        <v>50211502 View | Edit | Add opening stock | Delete</v>
+        <v>50211502</v>
       </c>
       <c r="C545" t="str">
         <v>BENSON MENTOLADOS</v>
@@ -16209,7 +16209,7 @@
         <v>67</v>
       </c>
       <c r="B546" t="str">
-        <v>11111137 View | Edit | Add opening stock | Delete</v>
+        <v>11111137</v>
       </c>
       <c r="C546" t="str">
         <v>BARRA DE SONIDO DAEWOO</v>
@@ -16238,7 +16238,7 @@
         <v>65</v>
       </c>
       <c r="B547" t="str">
-        <v>11111136 View | Edit | Add opening stock | Delete</v>
+        <v>11111136</v>
       </c>
       <c r="C547" t="str">
         <v>BAFLE 2X10 VIOS</v>
@@ -16267,7 +16267,7 @@
         <v>64</v>
       </c>
       <c r="B548" t="str">
-        <v>50161814 View | Edit | Add opening stock | Delete</v>
+        <v>50161814</v>
       </c>
       <c r="C548" t="str">
         <v>AZUCAR GENUINO MOSC</v>
@@ -16296,7 +16296,7 @@
         <v>58</v>
       </c>
       <c r="B549" t="str">
-        <v>50467007 View | Edit | Add opening stock | Delete</v>
+        <v>50467007</v>
       </c>
       <c r="C549" t="str">
         <v>ATUN ACEITE LATA CH</v>
@@ -16325,7 +16325,7 @@
         <v>57</v>
       </c>
       <c r="B550" t="str">
-        <v>50121500 View | Edit | Add opening stock | Delete</v>
+        <v>50121500</v>
       </c>
       <c r="C550" t="str">
         <v>ATUN</v>
@@ -16354,7 +16354,7 @@
         <v>55</v>
       </c>
       <c r="B551" t="str">
-        <v>50307000 View | Edit | Add opening stock | Delete</v>
+        <v>50307000</v>
       </c>
       <c r="C551" t="str">
         <v>ATE DE TEJOCOTE</v>
@@ -16383,7 +16383,7 @@
         <v>45</v>
       </c>
       <c r="B552" t="str">
-        <v>11111133 View | Edit | Add opening stock | Delete</v>
+        <v>11111133</v>
       </c>
       <c r="C552" t="str">
         <v>AROMATIZANTE GLADE</v>
@@ -16412,7 +16412,7 @@
         <v>28</v>
       </c>
       <c r="B553" t="str">
-        <v>50401500 View | Edit | Add opening stock | Delete</v>
+        <v>50401500</v>
       </c>
       <c r="C553" t="str">
         <v>ALCACHOFA PZ</v>
@@ -16441,7 +16441,7 @@
         <v>22</v>
       </c>
       <c r="B554" t="str">
-        <v>50403800 View | Edit | Add opening stock | Delete</v>
+        <v>50403800</v>
       </c>
       <c r="C554" t="str">
         <v>AJO BOTE CH</v>
@@ -16470,7 +16470,7 @@
         <v>18</v>
       </c>
       <c r="B555" t="str">
-        <v>50202300 View | Edit | Add opening stock | Delete</v>
+        <v>50202300</v>
       </c>
       <c r="C555" t="str">
         <v>AGUA SABOR</v>
@@ -16499,7 +16499,7 @@
         <v>14</v>
       </c>
       <c r="B556" t="str">
-        <v>52151505 View | Edit | Add opening stock | Delete</v>
+        <v>52151505</v>
       </c>
       <c r="C556" t="str">
         <v>AGITADOR</v>
@@ -16528,7 +16528,7 @@
         <v>12</v>
       </c>
       <c r="B557" t="str">
-        <v>50131801 View | Edit | Add opening stock | Delete</v>
+        <v>50131801</v>
       </c>
       <c r="C557" t="str">
         <v>ADOBERA SANDRITA</v>
@@ -16557,7 +16557,7 @@
         <v>3</v>
       </c>
       <c r="B558" t="str">
-        <v>50151500 View | Edit | Add opening stock | Delete</v>
+        <v>50151500</v>
       </c>
       <c r="C558" t="str">
         <v>ACE OLIVA OLI 750ML</v>
